--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>In Progress (batch 1)</t>
+          <t>Built - polish pass done</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>In Progress (batch 1)</t>
+          <t>Not started - no directory</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -672,7 +672,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>In Progress (batch 1)</t>
+          <t>Built - DPR fix applied</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>In Progress (batch 1)</t>
+          <t>Built - polish pending</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>In Progress (batch 1)</t>
+          <t>Built - polish pending</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Deferred (later batch)</t>
+          <t>Built - polish pending</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Deferred (later batch)</t>
+          <t>Not started - no directory</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -927,7 +927,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>In Progress (batch 1)</t>
+          <t>Built - Phaser audit pending</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Deferred (later batch)</t>
+          <t>Built - Phaser audit pending</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do-Not-Repeat Catalog" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -886,103 +886,197 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Archery / angle shooter (Bowman style)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/game/bowman</t>
-        </is>
-      </c>
+          <t>Tarzan rope-swing physics traversal (original, rope-swing-style)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Precision coverage against risks</t>
+          <t>Bridging life's gaps - momentum of continuous protection</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Coverage Archer</t>
+          <t>Rope Swing</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Guardian Archer</t>
+          <t>Swing to Secure</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+          <t>Approved - new original concept</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>coverage-archer</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Revamp</t>
+          <t>swing-to-secure</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Built - Phaser audit pending</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>5037</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Balance runner on a wire</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
-        </is>
-      </c>
+          <t>Crossy Road / Frogger lane-hopping (original, Crossy-Road-style)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Balancing family finances &amp; risks</t>
+          <t>Navigating life's risks to reach each life milestone</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Wire Runner / Balance Dodger</t>
+          <t>Life Crossing</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tightrope Protection</t>
+          <t>Milestone Hopper</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+          <t>Approved - new original concept</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>milestone-hopper</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>5038</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Archery / angle shooter (Bowman style)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/bowman</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Precision coverage against risks</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Coverage Archer</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Guardian Archer</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>coverage-archer</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Revamp</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Built - Phaser audit pending</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Balance runner on a wire</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Balancing family finances &amp; risks</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Wire Runner / Balance Dodger</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Tightrope Protection</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>tightrope-protection</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Revamp</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Built - Phaser audit pending</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1020,7 +1114,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>guardian-shelter (shield physics), secure-journey (rail shooter), smart-match-3d (triple match), risk-exit (arrow puzzle), life-soar (glider), coverage-archer (archery), tightrope-protection (balance runner). Approved but not yet scaffolded: balance-block-journey, shield-cascade</t>
+          <t>guardian-shelter (shield physics), secure-journey (rail shooter), smart-match-3d (triple match), risk-exit (arrow puzzle), life-soar (glider), coverage-archer (archery), tightrope-protection (balance runner), swing-to-secure (rope-swing traversal), milestone-hopper (lane-hopper). Approved but not yet scaffolded: balance-block-journey, shield-cascade</t>
         </is>
       </c>
     </row>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do-Not-Repeat Catalog" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -980,103 +980,432 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Archery / angle shooter (Bowman style)</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/game/bowman</t>
-        </is>
-      </c>
+          <t>1010! drag-and-place block puzzle (no gravity)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Precision coverage against risks</t>
+          <t>Asset allocation - fitting every asset class into a balanced portfolio</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Coverage Archer</t>
+          <t>Block Fit 1010</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Guardian Archer</t>
+          <t>Portfolio Fit</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>coverage-archer</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>Revamp</t>
+          <t>portfolio-fit</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Built - Phaser audit pending</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t>Built - review clean (restored)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>5044</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Balance runner on a wire</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
-        </is>
-      </c>
+          <t>Helix-jump descending ball</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Balancing family finances &amp; risks</t>
+          <t>Riding market cycles - descend through volatility, avoid the crash zones</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Wire Runner / Balance Dodger</t>
+          <t>Helix Descent</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tightrope Protection</t>
+          <t>Spiral Sprint</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+          <t>Approved - new original concept</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>spiral-sprint</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>In Progress (building)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>5048</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Plinko / pachinko board drop</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Market volatility &amp; ULIP - disciplined investing through ups and downs</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Plinko Pachinko</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Drop</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>wealth-drop</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>In Progress (building)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>5039</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>One-tap chain reaction</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>One policy protects many - the ripple effect of family coverage</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Chain Reaction</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Ripple Shield</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>ripple-shield</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>In Progress (building)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>5046</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Jenga-style block removal without toppling</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>De-risking your portfolio without destabilizing your life plan</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Jenga De-Risk</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Steady Tower</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>steady-tower</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>In Progress (building)</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>5047</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Orbit-switch timing arcade</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Staying on track - disciplined orbit around your life goals</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Orbit Hop</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Goal Orbit</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>goal-orbit</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>In Progress (building)</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>5050</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Flick bowling physics</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Knock out risks in one decisive shot - comprehensive cover</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Shield Bowling</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Risk Strike</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>risk-strike</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>In Progress (building)</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>5054</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Archery / angle shooter (Bowman style)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/bowman</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Precision coverage against risks</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Coverage Archer</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Guardian Archer</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>coverage-archer</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Revamp</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Built - Phaser audit pending</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Balance runner on a wire</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Balancing family finances &amp; risks</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Wire Runner / Balance Dodger</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Tightrope Protection</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>tightrope-protection</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Revamp</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Built - Phaser audit pending</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K12"/>
+  <autoFilter ref="A1:K19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1114,7 +1443,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>guardian-shelter (shield physics), secure-journey (rail shooter), smart-match-3d (triple match), risk-exit (arrow puzzle), life-soar (glider), coverage-archer (archery), tightrope-protection (balance runner), swing-to-secure (rope-swing traversal), milestone-hopper (lane-hopper). Approved but not yet scaffolded: balance-block-journey, shield-cascade</t>
+          <t>guardian-shelter (shield physics), secure-journey (rail shooter), smart-match-3d (triple match), risk-exit (arrow puzzle), life-soar (glider), coverage-archer (archery), tightrope-protection (balance runner), swing-to-secure (rope-swing traversal), milestone-hopper (lane-hopper), portfolio-fit (1010 block fit — restored after sign-off), spiral-sprint (helix jump), wealth-drop (plinko), ripple-shield (chain reaction), steady-tower (jenga de-risk), goal-orbit (orbit hop), risk-strike (flick bowling). Approved but not yet scaffolded: balance-block-journey, shield-cascade</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1455,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Dropped by feedback: Compound Quest (compound-merge), Shield Spin (shield-spin) — 'Already taken'. Removed for lacking BajajLife sign-off: life-goals-bubble-shooter, stackibility-stack, retire-rich-clicker, edurise-jumper, tax-save-maze, she-shield-protector, safe-stride-balancer, portfolio-fit, premium-tiles, income-flow, shield-drop</t>
+          <t>Dropped by feedback: Compound Quest (compound-merge), Shield Spin (shield-spin) — 'Already taken'. Removed for lacking BajajLife sign-off: life-goals-bubble-shooter, stackibility-stack, retire-rich-clicker, edurise-jumper, tax-save-maze, she-shield-protector, safe-stride-balancer, premium-tiles, income-flow, shield-drop. (portfolio-fit was later signed off and restored.)</t>
         </is>
       </c>
     </row>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -1064,7 +1064,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>In Progress (building)</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>In Progress (building)</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>In Progress (building)</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>In Progress (building)</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>In Progress (building)</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>In Progress (building)</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do-Not-Repeat Catalog" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1309,103 +1309,613 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Archery / angle shooter (Bowman style)</t>
+          <t>Pinball flippers (portrait single-screen table)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/game/bowman</t>
+          <t>Original concept</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Precision coverage against risks</t>
+          <t>Keeping the family's cover in play - every save at the flippers is a premium paid on time</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Coverage Archer</t>
+          <t>Premium Pinball</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Guardian Archer</t>
+          <t>Premium Pinball</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+          <t>Approved - new original concept</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>coverage-archer</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Revamp</t>
+          <t>premium-pinball</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Built - Phaser audit pending</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t>Built - final fix round in progress</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>5055</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Balance runner on a wire</t>
+          <t>Cricket batting timing (tap-to-swing chase)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+          <t>Original concept</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Balancing family finances &amp; risks</t>
+          <t>Every ball is a life event - cover it with the right timing</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Wire Runner / Balance Dodger</t>
+          <t>Cover Drive</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Tightrope Protection</t>
+          <t>Cover Drive</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+          <t>Approved - new original concept</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>cover-drive</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>5056</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Penalty-save reaction (swipe-to-dive zones)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Cover standing between risk and the family's goals - every save is cover doing its job</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Goal Keeper</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Goal Keeper</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>goal-keeper</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>5057</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Carrom flick-pocket physics (drag striker, pull to aim)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Pocket every goal - the Queen of Protection only stays yours if you cover her</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Carrom</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Carrom</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>wealth-carrom</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>5058</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Press-your-luck inflate (hold to grow, release to bank)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Grow wealth as far as you dare - a Term Shield absorbs the one burst you never saw coming</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Balloon</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Balloon</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>wealth-balloon</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>5059</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Pipe-rotation flow routing puzzle</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Route every rupee of income to the goals that matter - seal the leaks before payday flows</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Income Pipeline</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Income Pipeline</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>income-pipeline</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>5060</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Conveyor swipe-sorting (protect / grow / bin)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Protect it, grow it, or bin it - sort your money life before it scrolls past</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Smart Sorter</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Smart Sorter</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>smart-sorter</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>5061</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Traffic-control tap go/stop (junction management)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Life's traffic never stops - one Claim Cushion, and after that timing is everything</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Safe Crossing</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Safe Crossing</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>safe-crossing</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>5062</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Ice-slide pathing puzzle (swipe, glide to wall)</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>One swipe at a time, glide your shield past thin ice and bring it home to the family</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Slide to Safety</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Slide to Safety</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>slide-to-safety</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>5063</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Stop-the-marker precision timing</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Pay every premium right on time from 25 to 60 - discipline today is a pension tomorrow</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Perfect Premium</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Perfect Premium</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>perfect-premium</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>5064</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Archery / angle shooter (Bowman style)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/bowman</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Precision coverage against risks</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Coverage Archer</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Guardian Archer</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>coverage-archer</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Revamp</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Built - Phaser audit pending</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Balance runner on a wire</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Balancing family finances &amp; risks</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Wire Runner / Balance Dodger</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Tightrope Protection</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>tightrope-protection</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>Revamp</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Built - Phaser audit pending</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K19"/>
+  <autoFilter ref="A1:K29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1443,7 +1953,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>guardian-shelter (shield physics), secure-journey (rail shooter), smart-match-3d (triple match), risk-exit (arrow puzzle), life-soar (glider), coverage-archer (archery), tightrope-protection (balance runner), swing-to-secure (rope-swing traversal), milestone-hopper (lane-hopper), portfolio-fit (1010 block fit — restored after sign-off), spiral-sprint (helix jump), wealth-drop (plinko), ripple-shield (chain reaction), steady-tower (jenga de-risk), goal-orbit (orbit hop), risk-strike (flick bowling). Approved but not yet scaffolded: balance-block-journey, shield-cascade</t>
+          <t>guardian-shelter (shield physics), secure-journey (rail shooter), smart-match-3d (triple match), risk-exit (arrow puzzle), life-soar (glider), coverage-archer (archery), tightrope-protection (balance runner), swing-to-secure (rope-swing traversal), milestone-hopper (lane-hopper), portfolio-fit (1010 block fit — restored after sign-off), spiral-sprint (helix jump), wealth-drop (plinko), ripple-shield (chain reaction), steady-tower (jenga de-risk), goal-orbit (orbit hop), risk-strike (flick bowling), premium-pinball (pinball flippers), cover-drive (cricket batting timing), goal-keeper (penalty-save reaction), wealth-carrom (carrom flick-pocket), wealth-balloon (press-your-luck inflate), income-pipeline (pipe-rotation flow routing), smart-sorter (conveyor swipe-sorting), safe-crossing (traffic-control tap go/stop), slide-to-safety (ice-slide pathing), perfect-premium (stop-the-marker precision). Approved but not yet scaffolded: balance-block-journey, shield-cascade</t>
         </is>
       </c>
     </row>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do-Not-Repeat Catalog" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1819,103 +1819,358 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Archery / angle shooter (Bowman style)</t>
+          <t>One-tap impulse flight through gates (flappy-style)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/game/bowman</t>
+          <t>Original concept</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Precision coverage against risks</t>
+          <t>Life's expenses keep coming - keep your cover airborne and glide through every one</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Coverage Archer</t>
+          <t>Steady Wings</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Guardian Archer</t>
+          <t>Steady Wings</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+          <t>Approved - new original concept</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>coverage-archer</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Revamp</t>
+          <t>steady-wings</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Built - Phaser audit pending</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t>In build - agent running</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>5065</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Balance runner on a wire</t>
+          <t>Beat-synchronised rhythm tapping (radial go/no-go)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+          <t>Original concept</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Balancing family finances &amp; risks</t>
+          <t>A premium on every beat - stay in rhythm, skip the temptations, and cover never misses</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Wire Runner / Balance Dodger</t>
+          <t>Premium Pulse</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Tightrope Protection</t>
+          <t>Premium Pulse</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+          <t>Approved - new original concept</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>premium-pulse</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>In build - agent running</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>5066</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Simon-style serial sequence recall (ordered memory)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>A financial plan only works if you remember every step - recall it in order, skip the risky detours</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Smart Recall</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Smart Recall</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>smart-recall</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>In build - agent running</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>5067</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Tap-to-bounce juggling keep-ups (multi-body physics)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Real life means keeping every goal in the air at once - cover is what catches the one you miss</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Goal Juggler</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Goal Juggler</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>goal-juggler</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>In build - agent running</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>5068</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>WarioWare-style microgame rush (3-5s one-verb challenges)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Life comes at you fast - pay, protect, pick and plan in seconds; that is what good cover feels like</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Life Rush</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Life Rush</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>life-rush</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>In build - agent running</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>5069</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Archery / angle shooter (Bowman style)</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/bowman</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Precision coverage against risks</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Coverage Archer</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Guardian Archer</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>coverage-archer</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Revamp</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Built - Phaser audit pending</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Balance runner on a wire</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Balancing family finances &amp; risks</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Wire Runner / Balance Dodger</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tightrope Protection</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
           <t>tightrope-protection</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>Revamp</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Built - Phaser audit pending</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K29"/>
+  <autoFilter ref="A1:K34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -1350,7 +1350,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Built - final fix round in progress</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>In build - agent running</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>In build - agent running</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>In build - agent running</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -2013,7 +2013,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>In build - agent running</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>In build - agent running</t>
+          <t>Built - review clean</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>guardian-shelter (shield physics), secure-journey (rail shooter), smart-match-3d (triple match), risk-exit (arrow puzzle), life-soar (glider), coverage-archer (archery), tightrope-protection (balance runner), swing-to-secure (rope-swing traversal), milestone-hopper (lane-hopper), portfolio-fit (1010 block fit — restored after sign-off), spiral-sprint (helix jump), wealth-drop (plinko), ripple-shield (chain reaction), steady-tower (jenga de-risk), goal-orbit (orbit hop), risk-strike (flick bowling), premium-pinball (pinball flippers), cover-drive (cricket batting timing), goal-keeper (penalty-save reaction), wealth-carrom (carrom flick-pocket), wealth-balloon (press-your-luck inflate), income-pipeline (pipe-rotation flow routing), smart-sorter (conveyor swipe-sorting), safe-crossing (traffic-control tap go/stop), slide-to-safety (ice-slide pathing), perfect-premium (stop-the-marker precision). Approved but not yet scaffolded: balance-block-journey, shield-cascade</t>
+          <t>guardian-shelter (shield physics), secure-journey (rail shooter), smart-match-3d (triple match), risk-exit (arrow puzzle), life-soar (glider), coverage-archer (archery), tightrope-protection (balance runner), swing-to-secure (rope-swing traversal), milestone-hopper (lane-hopper), portfolio-fit (1010 block fit — restored after sign-off), spiral-sprint (helix jump), wealth-drop (plinko), ripple-shield (chain reaction), steady-tower (jenga de-risk), goal-orbit (orbit hop), risk-strike (flick bowling), premium-pinball (pinball flippers), cover-drive (cricket batting timing), goal-keeper (penalty-save reaction), wealth-carrom (carrom flick-pocket), wealth-balloon (press-your-luck inflate), income-pipeline (pipe-rotation flow routing), smart-sorter (conveyor swipe-sorting), safe-crossing (traffic-control tap go/stop), slide-to-safety (ice-slide pathing), perfect-premium (stop-the-marker precision), steady-wings (one-tap impulse flight), premium-pulse (beat-synced rhythm tapping), smart-recall (Simon serial sequence recall), goal-juggler (tap-to-bounce juggling keep-ups), life-rush (rapid-fire microgame rush). Approved but not yet scaffolded: balance-block-journey, shield-cascade</t>
         </is>
       </c>
     </row>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do-Not-Repeat Catalog" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2074,103 +2074,358 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Archery / angle shooter (Bowman style)</t>
+          <t>Archero-style arena survivor (stop-to-shoot, wave upgrades)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/game/bowman</t>
+          <t>https://apps.apple.com/app/archero/id1453651052</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Precision coverage against risks</t>
+          <t>Layered protection - every upgrade between waves is another rider on the family's cover</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Coverage Archer</t>
+          <t>Guardian Arena</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Guardian Archer</t>
+          <t>Guardian Arena</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>coverage-archer</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Revamp</t>
+          <t>guardian-arena</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Built - Phaser audit pending</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>5070</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Balance runner on a wire</t>
+          <t>Piano Tiles-style 4-lane melody tapper</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+          <t>https://apps.apple.com/app/piano-tiles-2/id1027688889</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Balancing family finances &amp; risks</t>
+          <t>A premium on every note - never miss a payment and the family's plan plays like music</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Wire Runner / Balance Dodger</t>
+          <t>Premium Tiles</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tightrope Protection</t>
+          <t>Premium Tiles</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: an earlier premium-tiles concept was removed in the 2026-07-28 scope cut for lacking sign-off; this is a fresh implementation of the explicitly requested piano-tiles genre</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>premium-tiles</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>5071</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Suika-style drop-and-merge collector (physics jar)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/app/suika-game-aladdin-x/id6444114954</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Compounding in your hands - small savings merge into life goals</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Merge</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Merge</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>wealth-merge</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>5072</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Fruit Ninja-style swipe slicer (slash risks, spare shields)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/app/fruit-ninja/id362949845</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Cut the risks out of the family's life - cover is the blade</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Risk Slash</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Risk Slash</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a fruit-slice game; this differentiates via the protect-the-Family-Shield rule (slicing blue shield orbs is the penalty) and risk-labelled targets</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>risk-slash</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>5073</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Ketchapp Stack-style timing tower (trim on miss, regrow on perfects)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/app/stack/id1080487957</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Every layer is a monthly SIP - discipline compounds, and consistency repairs old mistakes</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>SIP Stack</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>SIP Stack</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a stacking game; this differentiates via SIP milestone framing and the perfect-streak width-regrowth loop</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>sip-stack</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>5074</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Archery / angle shooter (Bowman style)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/bowman</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Precision coverage against risks</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Coverage Archer</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Guardian Archer</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>coverage-archer</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Revamp</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Built - Phaser audit pending</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Balance runner on a wire</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Balancing family finances &amp; risks</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Wire Runner / Balance Dodger</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Tightrope Protection</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>tightrope-protection</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>Revamp</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Built - Phaser audit pending</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2181,7 +2436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2215,34 +2470,46 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Removed from repo</t>
+          <t>This repo (proposed, pending sign-off)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Dropped by feedback: Compound Quest (compound-merge), Shield Spin (shield-spin) — 'Already taken'. Removed for lacking BajajLife sign-off: life-goals-bubble-shooter, stackibility-stack, retire-rich-clicker, edurise-jumper, tax-save-maze, she-shield-protector, safe-stride-balancer, premium-tiles, income-flow, shield-drop. (portfolio-fit was later signed off and restored.)</t>
+          <t>Batch 6 (2026-07-29): guardian-arena (Archero-style arena survivor), premium-tiles (piano-tiles melody lane tapper), wealth-merge (suika drop-merge collector), risk-slash (swipe slicer with protect-the-shield rule; note game-store has fruit-slice), sip-stack (stack timing tower with SIP framing; note game-store has stacking)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>bajaj-game-store (do not repeat)</t>
+          <t>Removed from repo</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>snake, hangman, word scramble, match-3 x2, tetris, fruit-slice, runners/climbers x4, top-down shooter, bomberman, galaga, sudoku x2, whack-a-mole x2, brick-breaker, jigsaw x2, minesweeper, racing, tube-sorting, quiz x3, bubble shooter, peg solitaire, stacking, memory-flip, tower defense, snakes &amp; ladders, arcade dodger</t>
+          <t>Dropped by feedback: Compound Quest (compound-merge), Shield Spin (shield-spin) — 'Already taken'. Removed for lacking BajajLife sign-off: life-goals-bubble-shooter, stackibility-stack, retire-rich-clicker, edurise-jumper, tax-save-maze, she-shield-protector, safe-stride-balancer, premium-tiles, income-flow, shield-drop. (portfolio-fit was later signed off and restored.)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>bajaj-game-store (do not repeat)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>snake, hangman, word scramble, match-3 x2, tetris, fruit-slice, runners/climbers x4, top-down shooter, bomberman, galaga, sudoku x2, whack-a-mole x2, brick-breaker, jigsaw x2, minesweeper, racing, tube-sorting, quiz x3, bubble shooter, peg solitaire, stacking, memory-flip, tower defense, snakes &amp; ladders, arcade dodger</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Dropped by feedback</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Wealth Current (physics orb), Path to Legacy (line drawing), Launch to Protection (hedgehog launch), Secure Foundations (falling sand)</t>
         </is>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do-Not-Repeat Catalog" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2329,103 +2329,338 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Archery / angle shooter (Bowman style)</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/game/bowman</t>
-        </is>
-      </c>
+          <t>Time-loop past-self co-op (previous runs replay as live ghost helpers)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Precision coverage against risks</t>
+          <t>Your past contributions keep working for you - every premium your past self paid protects the family today</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Coverage Archer</t>
+          <t>Legacy Echo</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Guardian Archer</t>
+          <t>Legacy Echo</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>coverage-archer</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Revamp</t>
+          <t>legacy-echo</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Built - Phaser audit pending</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>5075</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Balance runner on a wire</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
-        </is>
-      </c>
+          <t>Time moves only when you move (SUPERHOT rule)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Balancing family finances &amp; risks</t>
+          <t>Good cover buys you time to think - slow life down and pick your path</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Wire Runner / Balance Dodger</t>
+          <t>Time Shield</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Tightrope Protection</t>
+          <t>Time Shield</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
+          <t>time-shield</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>5076</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Qix/JezzBall territory capture (claim ground, wall risks out)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Ring-fence the family's wealth - a real asset-protection term made playable</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Ring-Fence</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Ring-Fence</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>ring-fence</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>5077</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Darkness + sonar pulse navigation (perception as a resource)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>You cannot see risks coming - your cover can; send the radar, read the danger, walk the family home</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Risk Radar</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Risk Radar</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>risk-radar</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>5078</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Duet-style twin-orbit dodger (one input, two coupled avatars)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Protection and growth are two sides of one plan - steer them together; losing either loses the future</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Dual Cover</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Dual Cover</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>dual-cover</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Archery / angle shooter (Bowman style)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/bowman</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Precision coverage against risks</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Coverage Archer</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Guardian Archer</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>coverage-archer</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Revamp</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Built - Phaser audit pending</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Balance runner on a wire</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Balancing family finances &amp; risks</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Wire Runner / Balance Dodger</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Tightrope Protection</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>tightrope-protection</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>Revamp</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Built - Phaser audit pending</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K39"/>
+  <autoFilter ref="A1:K44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2475,7 +2710,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Batch 6 (2026-07-29): guardian-arena (Archero-style arena survivor), premium-tiles (piano-tiles melody lane tapper), wealth-merge (suika drop-merge collector), risk-slash (swipe slicer with protect-the-shield rule; note game-store has fruit-slice), sip-stack (stack timing tower with SIP framing; note game-store has stacking)</t>
+          <t>Batch 6 (2026-07-29): guardian-arena (Archero-style arena survivor), premium-tiles (piano-tiles melody lane tapper), wealth-merge (suika drop-merge collector), risk-slash (swipe slicer with protect-the-shield rule; note game-store has fruit-slice), sip-stack (stack timing tower with SIP framing; note game-store has stacking). Batch 7 (2026-07-30): legacy-echo (time-loop past-self co-op), time-shield (time moves only when you move), ring-fence (Qix territory capture), risk-radar (darkness + sonar pulse navigation), dual-cover (Duet twin-orbit dodger)</t>
         </is>
       </c>
     </row>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do-Not-Repeat Catalog" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - 2026-08-03 review: hop moved onTap-&gt;pointerdown, double-fire and unavoidable-death fixed; casual 46-&gt;58.5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1121,23 +1121,23 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>One-tap chain reaction</t>
+          <t>Jenga-style block removal without toppling</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>One policy protects many - the ripple effect of family coverage</t>
+          <t>De-risking your portfolio without destabilizing your life plan</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Chain Reaction</t>
+          <t>Jenga De-Risk</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Ripple Shield</t>
+          <t>Steady Tower</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>ripple-shield</t>
+          <t>steady-tower</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>5046</v>
+        <v>5047</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Jenga-style block removal without toppling</t>
+          <t>Orbit-switch timing arcade</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>De-risking your portfolio without destabilizing your life plan</t>
+          <t>Staying on track - disciplined orbit around your life goals</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Jenga De-Risk</t>
+          <t>Orbit Hop</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Steady Tower</t>
+          <t>Goal Orbit</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>steady-tower</t>
+          <t>goal-orbit</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1209,29 +1209,29 @@
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>5047</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Orbit-switch timing arcade</t>
+          <t>Flick bowling physics</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Staying on track - disciplined orbit around your life goals</t>
+          <t>Knock out risks in one decisive shot - comprehensive cover</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Orbit Hop</t>
+          <t>Shield Bowling</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Goal Orbit</t>
+          <t>Risk Strike</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>goal-orbit</t>
+          <t>risk-strike</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1256,29 +1256,33 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>5050</v>
+        <v>5054</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Flick bowling physics</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n"/>
+          <t>Pinball flippers (portrait single-screen table)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Knock out risks in one decisive shot - comprehensive cover</t>
+          <t>Keeping the family's cover in play - every save at the flippers is a premium paid on time</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Shield Bowling</t>
+          <t>Premium Pinball</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Risk Strike</t>
+          <t>Premium Pinball</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1289,7 +1293,7 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>risk-strike</t>
+          <t>premium-pinball</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>5054</v>
+        <v>5055</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Pinball flippers (portrait single-screen table)</t>
+          <t>Cricket batting timing (tap-to-swing chase)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1319,17 +1323,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Keeping the family's cover in play - every save at the flippers is a premium paid on time</t>
+          <t>Every ball is a life event - cover it with the right timing</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Premium Pinball</t>
+          <t>Cover Drive</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Premium Pinball</t>
+          <t>Cover Drive</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1340,7 +1344,7 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>premium-pinball</t>
+          <t>cover-drive</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1350,17 +1354,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - 2026-08-03 review: swept bat/ball collision added (there was none; 4.3% of "hits" touched the blade); 4450/4450 perfect swings connect</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>5055</v>
+        <v>5056</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Cricket batting timing (tap-to-swing chase)</t>
+          <t>Steer a decaying cover span; renew before the event locks</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1370,28 +1374,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Every ball is a life event - cover it with the right timing</t>
+          <t>Cover is bought in advance, lapses if unrenewed, and never stretches over everything at once</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Cover Drive</t>
+          <t>Goal Keeper</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Cover Drive</t>
+          <t>Goal Keeper</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Approved - new original concept</t>
+          <t>Rebuilt 2026-08-03 - BajajLife review found the original concept and execution incorrect</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>cover-drive</t>
+          <t>goal-keeper</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1401,17 +1405,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Rebuilt - 2026-08-03 review: cover-span mechanic; never-renew 0.0% vs renew 99.3%; gate PASS</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>5056</v>
+        <v>5057</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Penalty-save reaction (swipe-to-dive zones)</t>
+          <t>Carrom flick-pocket physics (drag striker, pull to aim)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1421,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Cover standing between risk and the family's goals - every save is cover doing its job</t>
+          <t>Pocket every goal - the Queen of Protection only stays yours if you cover her</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Goal Keeper</t>
+          <t>Wealth Carrom</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Goal Keeper</t>
+          <t>Wealth Carrom</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1442,7 +1446,7 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>goal-keeper</t>
+          <t>wealth-carrom</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1452,17 +1456,17 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - 2026-08-03 review: bot opponent shipped, 0 tunnelling in 452,813 ticks; 89.4/71.9/55.0% by difficulty</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>5057</v>
+        <v>5058</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Carrom flick-pocket physics (drag striker, pull to aim)</t>
+          <t>Goal-funding triage with forecast shocks and a fixed-premium cover decision</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1472,28 +1476,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Pocket every goal - the Queen of Protection only stays yours if you cover her</t>
+          <t>A fixed premium against a proportional loss - cover is worth buying on the big position, not the small one</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Wealth Carrom</t>
+          <t>Wealth Balloon</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Wealth Carrom</t>
+          <t>Wealth Balloon</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Approved - new original concept</t>
+          <t>Mechanic replaced 2026-08-03 - BajajLife review found press-your-luck provided no meaningful value; the old gate measured a zero-information bot at 55% of the skilled score</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>wealth-carrom</t>
+          <t>wealth-balloon</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1503,17 +1507,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Rebuilt - 2026-08-03 review: press-your-luck replaced with goal triage; skill gap 17.4pp -&gt; 87.5pp</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>5058</v>
+        <v>5059</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Press-your-luck inflate (hold to grow, release to bank)</t>
+          <t>Pipe-rotation flow routing puzzle</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1523,17 +1527,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Grow wealth as far as you dare - a Term Shield absorbs the one burst you never saw coming</t>
+          <t>Route every rupee of income to the goals that matter - seal the leaks before payday flows</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Wealth Balloon</t>
+          <t>Income Pipeline</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Wealth Balloon</t>
+          <t>Income Pipeline</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1544,7 +1548,7 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>wealth-balloon</t>
+          <t>income-pipeline</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1554,17 +1558,17 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - 2026-08-03 review fix: run no longer ends on a dry level 1 (18s -&gt; 91s); gate 82.3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5059</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Pipe-rotation flow routing puzzle</t>
+          <t>Conveyor swipe-sorting (protect / grow / bin)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1574,17 +1578,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Route every rupee of income to the goals that matter - seal the leaks before payday flows</t>
+          <t>Protect it, grow it, or bin it - sort your money life before it scrolls past</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Income Pipeline</t>
+          <t>Smart Sorter</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Income Pipeline</t>
+          <t>Smart Sorter</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1595,7 +1599,7 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>income-pipeline</t>
+          <t>smart-sorter</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1605,17 +1609,17 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - 2026-08-03 review fix: 3-card mistake grace (11s -&gt; 19s); gate PASS, casual 41.6%</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>5060</v>
+        <v>5061</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Conveyor swipe-sorting (protect / grow / bin)</t>
+          <t>Traffic-control tap go/stop (junction management)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1625,17 +1629,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Protect it, grow it, or bin it - sort your money life before it scrolls past</t>
+          <t>Life's traffic never stops - one Claim Cushion, and after that timing is everything</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Smart Sorter</t>
+          <t>Safe Crossing</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Smart Sorter</t>
+          <t>Safe Crossing</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1646,7 +1650,7 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>smart-sorter</t>
+          <t>safe-crossing</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1656,17 +1660,17 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - 2026-08-03 review: HUD off the traffic lane, bracket/triangle danger read; gate PASS unchanged</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>5061</v>
+        <v>5062</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Traffic-control tap go/stop (junction management)</t>
+          <t>Ice-slide pathing puzzle (swipe, glide to wall)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1676,17 +1680,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Life's traffic never stops - one Claim Cushion, and after that timing is everything</t>
+          <t>One swipe at a time, glide your shield past thin ice and bring it home to the family</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Safe Crossing</t>
+          <t>Slide to Safety</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Safe Crossing</t>
+          <t>Slide to Safety</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1697,7 +1701,7 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>safe-crossing</t>
+          <t>slide-to-safety</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1707,17 +1711,17 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - 2026-08-03 review: swept collision, 1600 slides 0 tunnelling; skilled 48.7% / random 0.0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>5062</v>
+        <v>5063</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Ice-slide pathing puzzle (swipe, glide to wall)</t>
+          <t>Rate-limited cover-level management against partially-hidden incoming claims</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1727,28 +1731,28 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>One swipe at a time, glide your shield past thin ice and bring it home to the family</t>
+          <t>Under-insuring is cheap until the event arrives; over-insuring is safe but spends money the goals needed</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Slide to Safety</t>
+          <t>Perfect Premium</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Slide to Safety</t>
+          <t>Perfect Premium</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Approved - new original concept</t>
+          <t>Rebuilt 2026-08-03 - BajajLife review found the experience did not feel like a game</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>slide-to-safety</t>
+          <t>perfect-premium</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1758,17 +1762,17 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Rebuilt - 2026-08-03 review: real-time cover management; skilled scores 13.5x random</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>5063</v>
+        <v>5064</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Stop-the-marker precision timing</t>
+          <t>One-tap impulse flight through gates (flappy-style)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1778,17 +1782,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Pay every premium right on time from 25 to 60 - discipline today is a pension tomorrow</t>
+          <t>Life's expenses keep coming - keep your cover airborne and glide through every one</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Perfect Premium</t>
+          <t>Steady Wings</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Perfect Premium</t>
+          <t>Steady Wings</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1799,7 +1803,7 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>perfect-premium</t>
+          <t>steady-wings</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1813,13 +1817,13 @@
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>5064</v>
+        <v>5065</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>One-tap impulse flight through gates (flappy-style)</t>
+          <t>Beat-synchronised rhythm tapping (radial go/no-go)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1829,17 +1833,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Life's expenses keep coming - keep your cover airborne and glide through every one</t>
+          <t>A premium on every beat - stay in rhythm, skip the temptations, and cover never misses</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Steady Wings</t>
+          <t>Premium Pulse</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Steady Wings</t>
+          <t>Premium Pulse</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1850,7 +1854,7 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>steady-wings</t>
+          <t>premium-pulse</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1864,13 +1868,13 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>5065</v>
+        <v>5066</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Beat-synchronised rhythm tapping (radial go/no-go)</t>
+          <t>Simon-style serial sequence recall (ordered memory)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1880,17 +1884,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>A premium on every beat - stay in rhythm, skip the temptations, and cover never misses</t>
+          <t>A financial plan only works if you remember every step - recall it in order, skip the risky detours</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Premium Pulse</t>
+          <t>Smart Recall</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Premium Pulse</t>
+          <t>Smart Recall</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1901,7 +1905,7 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>premium-pulse</t>
+          <t>smart-recall</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1911,17 +1915,17 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - 2026-08-03 review: opaque colorRest palette, labels sub-AA -&gt; 15.56:1; gate byte-identical</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>5066</v>
+        <v>5067</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Simon-style serial sequence recall (ordered memory)</t>
+          <t>WarioWare-style microgame rush (3-5s one-verb challenges)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1931,17 +1935,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>A financial plan only works if you remember every step - recall it in order, skip the risky detours</t>
+          <t>Life comes at you fast - pay, protect, pick and plan in seconds; that is what good cover feels like</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Smart Recall</t>
+          <t>Life Rush</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Smart Recall</t>
+          <t>Life Rush</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1952,7 +1956,7 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>smart-recall</t>
+          <t>life-rush</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1962,48 +1966,48 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - 2026-08-03 review: persistent instruction frame, countdown un-occluded; gate identical (rules unchanged)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>5067</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Tap-to-bounce juggling keep-ups (multi-body physics)</t>
+          <t>Archero-style arena survivor (stop-to-shoot, wave upgrades)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Original concept</t>
+          <t>https://apps.apple.com/app/archero/id1453651052</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Real life means keeping every goal in the air at once - cover is what catches the one you miss</t>
+          <t>Layered protection - every upgrade between waves is another rider on the family's cover</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Goal Juggler</t>
+          <t>Guardian Arena</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Goal Juggler</t>
+          <t>Guardian Arena</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Approved - new original concept</t>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>goal-juggler</t>
+          <t>guardian-arena</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2013,48 +2017,48 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - pending BajajLife sign-off</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>5068</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>WarioWare-style microgame rush (3-5s one-verb challenges)</t>
+          <t>Piano Tiles-style 4-lane melody tapper</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Original concept</t>
+          <t>https://apps.apple.com/app/piano-tiles-2/id1027688889</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Life comes at you fast - pay, protect, pick and plan in seconds; that is what good cover feels like</t>
+          <t>A premium on every note - never miss a payment and the family's plan plays like music</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Life Rush</t>
+          <t>Premium Tiles</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Life Rush</t>
+          <t>Premium Tiles</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Approved - new original concept</t>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: an earlier premium-tiles concept was removed in the 2026-07-28 scope cut for lacking sign-off; this is a fresh implementation of the explicitly requested piano-tiles genre</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>life-rush</t>
+          <t>premium-tiles</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -2064,37 +2068,37 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Built - review clean</t>
+          <t>Built - pending BajajLife sign-off</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
-        <v>5069</v>
+        <v>5071</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Archero-style arena survivor (stop-to-shoot, wave upgrades)</t>
+          <t>Suika-style drop-and-merge collector (physics jar)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://apps.apple.com/app/archero/id1453651052</t>
+          <t>https://apps.apple.com/app/suika-game-aladdin-x/id6444114954</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Layered protection - every upgrade between waves is another rider on the family's cover</t>
+          <t>Compounding in your hands - small savings merge into life goals</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Guardian Arena</t>
+          <t>Wealth Merge</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Guardian Arena</t>
+          <t>Wealth Merge</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2105,7 +2109,7 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>guardian-arena</t>
+          <t>wealth-merge</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2115,48 +2119,48 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Built - pending BajajLife sign-off</t>
+          <t>Built - 2026-08-03 review: bronze-&gt;diamond tier ladder (tier 5 used to read below tier 4); gate PASS + new tier-ladder guard</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
-        <v>5070</v>
+        <v>5072</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Piano Tiles-style 4-lane melody tapper</t>
+          <t>Fruit Ninja-style swipe slicer (slash risks, spare shields)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://apps.apple.com/app/piano-tiles-2/id1027688889</t>
+          <t>https://apps.apple.com/app/fruit-ninja/id362949845</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>A premium on every note - never miss a payment and the family's plan plays like music</t>
+          <t>Cut the risks out of the family's life - cover is the blade</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Premium Tiles</t>
+          <t>Risk Slash</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Premium Tiles</t>
+          <t>Risk Slash</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: an earlier premium-tiles concept was removed in the 2026-07-28 scope cut for lacking sign-off; this is a fresh implementation of the explicitly requested piano-tiles genre</t>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a fruit-slice game; this differentiates via the protect-the-Family-Shield rule (slicing blue shield orbs is the penalty) and risk-labelled targets</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>premium-tiles</t>
+          <t>risk-slash</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2170,44 +2174,44 @@
         </is>
       </c>
       <c r="K34" s="2" t="n">
-        <v>5071</v>
+        <v>5073</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Suika-style drop-and-merge collector (physics jar)</t>
+          <t>Ketchapp Stack-style timing tower (trim on miss, regrow on perfects)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://apps.apple.com/app/suika-game-aladdin-x/id6444114954</t>
+          <t>https://apps.apple.com/app/stack/id1080487957</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Compounding in your hands - small savings merge into life goals</t>
+          <t>Every layer is a monthly SIP - discipline compounds, and consistency repairs old mistakes</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Wealth Merge</t>
+          <t>SIP Stack</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Wealth Merge</t>
+          <t>SIP Stack</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Proposed 2026-07-29 - pending BajajLife sign-off</t>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a stacking game; this differentiates via SIP milestone framing and the perfect-streak width-regrowth loop</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>wealth-merge</t>
+          <t>sip-stack</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2217,48 +2221,44 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Built - pending BajajLife sign-off</t>
+          <t>Built - 2026-08-03 review: draw/collision geometry unified (224/224 at 0.000px); gate PASS</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>5072</v>
+        <v>5074</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fruit Ninja-style swipe slicer (slash risks, spare shields)</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>https://apps.apple.com/app/fruit-ninja/id362949845</t>
-        </is>
-      </c>
+          <t>Time-loop past-self co-op (previous runs replay as live ghost helpers)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Cut the risks out of the family's life - cover is the blade</t>
+          <t>Your past contributions keep working for you - every premium your past self paid protects the family today</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Risk Slash</t>
+          <t>Legacy Echo</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Risk Slash</t>
+          <t>Legacy Echo</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a fruit-slice game; this differentiates via the protect-the-Family-Shield rule (slicing blue shield orbs is the penalty) and risk-labelled targets</t>
+          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>risk-slash</t>
+          <t>legacy-echo</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -2268,48 +2268,44 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Built - pending BajajLife sign-off</t>
+          <t>Built - 2026-08-03 review: four competing mechanics deleted, in-game objective coach; gate 8/8</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>5073</v>
+        <v>5075</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Ketchapp Stack-style timing tower (trim on miss, regrow on perfects)</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>https://apps.apple.com/app/stack/id1080487957</t>
-        </is>
-      </c>
+          <t>Qix/JezzBall territory capture (claim ground, wall risks out)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Every layer is a monthly SIP - discipline compounds, and consistency repairs old mistakes</t>
+          <t>Ring-fence the family's wealth - a real asset-protection term made playable</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>SIP Stack</t>
+          <t>Ring-Fence</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>SIP Stack</t>
+          <t>Ring-Fence</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a stacking game; this differentiates via SIP milestone framing and the perfect-streak width-regrowth loop</t>
+          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>sip-stack</t>
+          <t>ring-fence</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2319,33 +2315,33 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Built - pending BajajLife sign-off</t>
+          <t>Built - 2026-08-03 review: 128px dead strip removed, surveyor art direction; gate PASS</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>5074</v>
+        <v>5077</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Time-loop past-self co-op (previous runs replay as live ghost helpers)</t>
+          <t>Darkness + sonar pulse navigation (perception as a resource)</t>
         </is>
       </c>
       <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Your past contributions keep working for you - every premium your past self paid protects the family today</t>
+          <t>You cannot see risks coming - your cover can; send the radar, read the danger, walk the family home</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Legacy Echo</t>
+          <t>Risk Radar</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Legacy Echo</t>
+          <t>Risk Radar</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2356,7 +2352,7 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>legacy-echo</t>
+          <t>risk-radar</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -2366,301 +2362,113 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Built - pending BajajLife sign-off</t>
+          <t>Built - 2026-08-03 review: signal vocabulary, dotted-map compositing bug fixed; gate 16-&gt;21 checks</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5075</v>
+        <v>5078</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Time moves only when you move (SUPERHOT rule)</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n"/>
+          <t>Archery / angle shooter (Bowman style)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/bowman</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Good cover buys you time to think - slow life down and pick your path</t>
+          <t>Precision coverage against risks</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Time Shield</t>
+          <t>Coverage Archer</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Time Shield</t>
+          <t>Guardian Archer</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
+          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>time-shield</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
+          <t>coverage-archer</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Revamp</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Built - pending BajajLife sign-off</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>5076</v>
-      </c>
+          <t>Built - Phaser audit pending</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Qix/JezzBall territory capture (claim ground, wall risks out)</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n"/>
+          <t>Balance runner on a wire</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ring-fence the family's wealth - a real asset-protection term made playable</t>
+          <t>Balancing family finances &amp; risks</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Ring-Fence</t>
+          <t>Wire Runner / Balance Dodger</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Ring-Fence</t>
+          <t>Tightrope Protection</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
+          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>ring-fence</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
+          <t>tightrope-protection</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Revamp</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Built - pending BajajLife sign-off</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>5077</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Darkness + sonar pulse navigation (perception as a resource)</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>You cannot see risks coming - your cover can; send the radar, read the danger, walk the family home</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Risk Radar</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Risk Radar</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>risk-radar</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Built - pending BajajLife sign-off</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>5078</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Duet-style twin-orbit dodger (one input, two coupled avatars)</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Protection and growth are two sides of one plan - steer them together; losing either loses the future</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Dual Cover</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Dual Cover</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>dual-cover</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Built - pending BajajLife sign-off</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>5079</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Archery / angle shooter (Bowman style)</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/game/bowman</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Precision coverage against risks</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Coverage Archer</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Guardian Archer</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>coverage-archer</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Revamp</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
           <t>Built - Phaser audit pending</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Balance runner on a wire</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Balancing family finances &amp; risks</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Wire Runner / Balance Dodger</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Tightrope Protection</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>tightrope-protection</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Revamp</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Built - Phaser audit pending</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K44"/>
+  <autoFilter ref="A1:K40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2698,7 +2506,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>guardian-shelter (shield physics), secure-journey (rail shooter), smart-match-3d (triple match), risk-exit (arrow puzzle), life-soar (glider), coverage-archer (archery), tightrope-protection (balance runner), swing-to-secure (rope-swing traversal), milestone-hopper (lane-hopper), portfolio-fit (1010 block fit — restored after sign-off), spiral-sprint (helix jump), wealth-drop (plinko), ripple-shield (chain reaction), steady-tower (jenga de-risk), goal-orbit (orbit hop), risk-strike (flick bowling), premium-pinball (pinball flippers), cover-drive (cricket batting timing), goal-keeper (penalty-save reaction), wealth-carrom (carrom flick-pocket), wealth-balloon (press-your-luck inflate), income-pipeline (pipe-rotation flow routing), smart-sorter (conveyor swipe-sorting), safe-crossing (traffic-control tap go/stop), slide-to-safety (ice-slide pathing), perfect-premium (stop-the-marker precision), steady-wings (one-tap impulse flight), premium-pulse (beat-synced rhythm tapping), smart-recall (Simon serial sequence recall), goal-juggler (tap-to-bounce juggling keep-ups), life-rush (rapid-fire microgame rush). Approved but not yet scaffolded: balance-block-journey, shield-cascade</t>
+          <t>guardian-shelter (shield physics), secure-journey (rail shooter), smart-match-3d (triple match), risk-exit (arrow puzzle), life-soar (glider), coverage-archer (archery), tightrope-protection (balance runner), swing-to-secure (rope-swing traversal), milestone-hopper (lane-hopper), portfolio-fit (1010 block fit — restored after sign-off), spiral-sprint (helix jump), wealth-drop (plinko), steady-tower (jenga de-risk), goal-orbit (orbit hop), risk-strike (flick bowling), premium-pinball (pinball flippers), cover-drive (cricket batting timing), goal-keeper (penalty-save reaction), wealth-carrom (carrom flick-pocket), wealth-balloon (press-your-luck inflate), income-pipeline (pipe-rotation flow routing), smart-sorter (conveyor swipe-sorting), safe-crossing (traffic-control tap go/stop), slide-to-safety (ice-slide pathing), perfect-premium (stop-the-marker precision), steady-wings (one-tap impulse flight), premium-pulse (beat-synced rhythm tapping), smart-recall (Simon serial sequence recall), life-rush (rapid-fire microgame rush). Approved but not yet scaffolded: balance-block-journey, shield-cascade</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2518,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Batch 6 (2026-07-29): guardian-arena (Archero-style arena survivor), premium-tiles (piano-tiles melody lane tapper), wealth-merge (suika drop-merge collector), risk-slash (swipe slicer with protect-the-shield rule; note game-store has fruit-slice), sip-stack (stack timing tower with SIP framing; note game-store has stacking). Batch 7 (2026-07-30): legacy-echo (time-loop past-self co-op), time-shield (time moves only when you move), ring-fence (Qix territory capture), risk-radar (darkness + sonar pulse navigation), dual-cover (Duet twin-orbit dodger)</t>
+          <t>Batch 6 (2026-07-29): guardian-arena (Archero-style arena survivor), premium-tiles (piano-tiles melody lane tapper), wealth-merge (suika drop-merge collector), risk-slash (swipe slicer with protect-the-shield rule; note game-store has fruit-slice), sip-stack (stack timing tower with SIP framing; note game-store has stacking). Batch 7 (2026-07-30): legacy-echo (time-loop past-self co-op), ring-fence (Qix territory capture), risk-radar (darkness + sonar pulse navigation)</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2554,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Wealth Current (physics orb), Path to Legacy (line drawing), Launch to Protection (hedgehog launch), Secure Foundations (falling sand)</t>
+          <t>Wealth Current (physics orb), Path to Legacy (line drawing), Launch to Protection (hedgehog launch), Secure Foundations (falling sand). 2026-08-03 review: Dual Cover, Goal Juggler, Ripple Shield, Time Shield — directories deleted, ports 5079 / 5068 / 5046 / 5076 retired</t>
         </is>
       </c>
     </row>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -957,7 +957,11 @@
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The overall quality is below the expected standard." | RESOLVED - the hop was bound to the kit onTap, which fires on pointerup and charged every input the full 60-150ms contact; onSwipe was also wired, so one gesture fired two hops; and nothing checked destination occupancy, so ~35% of blind forward hops died with no counterplay. Casual win 46.0 -&gt; 58.5%, brisk 56.0 -&gt; 73.0%. Six milestones now bank a real corpus. The old debt sprite read as a handbag - rebuilt.</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>milestone-hopper</t>
@@ -1341,7 +1345,11 @@
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: batter misplaced, cannot hit reliably, collision inaccurate, no insurance objective, result screen off-template. | RESOLVED - there was NO collision test at all; shots were scored purely on tap timing against authored windows. Measured over 7,200 seeded deliveries, the blade actually touched the ball on 4.3% of the shots the game scored as hits. Replaced with swept segment-segment collision: 4450/4450 perfectly-timed swings now connect and middle. Four insurance zones with shaped payouts (Guaranteed Income provably cannot win alone). Result screen brought onto the shared template. EMAIL FIELD DELIBERATELY NOT ADDED - superseded by the repo-wide Name+Mobile decision.</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>cover-drive</t>
@@ -1392,7 +1400,11 @@
           <t>Rebuilt 2026-08-03 - BajajLife review found the original concept and execution incorrect</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The entire game concept and execution are incorrect", and separately (as "Goal Area") "looks completely AI-generated and lacks visual identity". Both notes are this one game. | REBUILT - the cover span, whose half-width IS the sum assured, decays every second and is renewable only before the event locks at 55% of ball flight. Measured: perfect positioning while never renewing wins 0.0%; identical positioning with renewals wins 99.3%. The reaction sweep is deliberately flat, so cover management separates players, not reflexes.</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>goal-keeper</t>
@@ -1443,7 +1455,11 @@
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: weak carrom design, no bot opponent, no proper sliding/flicking control. | RESOLVED - the controls and fixed-step physics already existed and worked; they were re-verified rather than rewritten. The bot genuinely did not exist: the ghost-ball planner was imported only by the balance sim, never by the shipped bundle, so the game was solo score-attack. Bot now ships at three difficulties (89.4 / 71.9 / 55.0% against a skilled reference, random 21.3 / 11.3 / 5.0%). Anti-tunnelling proven by swept closest-approach: 880 max-power strikes, 452,813 ticks, 0 pass-throughs. 0 draws in 960 matches.</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>wealth-carrom</t>
@@ -1494,7 +1510,11 @@
           <t>Mechanic replaced 2026-08-03 - BajajLife review found press-your-luck provided no meaningful value; the old gate measured a zero-information bot at 55% of the skilled score</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The selected game format does not provide meaningful value." | MECHANIC REPLACED - the old gate condemned it: a bot with zero information scored 55% of the skilled result, because hold-and-release has one degree of freedom per round. A hidden random burst threshold also told players their money evaporates unpredictably, the wrong message for an insurer. Now goal-funding triage with shocks forecast 4s ahead and a fixed-premium cover decision. Skill gap 17.4pp -&gt; 87.5pp.</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>wealth-balloon</t>
@@ -1545,7 +1565,11 @@
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The game is not functioning." | RESOLVED - no crash; it built clean and passed its gate while ending the run ~18s in, because a dry board called endRun and level 1 had an 18s clock, so boards 2 and 3 never appeared. A dry board now costs the level only; timers 26/28/32s; win bar moved off all-six-tanks (even the greedy bot clears that only 78% of the time). Run 18s -&gt; 91s.</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>income-pipeline</t>
@@ -1596,7 +1620,11 @@
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The game is not working." | RESOLVED - no crash, and input was fine (a scripted drag moved the score). 3 lives against 12 unfamiliar item types at 1.9s/card killed a first-timer on the opening three cards; run over in 11s. Added a 3-card grace that still flashes red and breaks combo but cannot spend a life. Budget stays 3 - raising it to 5 sent the casual bot to 83.4%, outside the 25-45% band.</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>smart-sorter</t>
@@ -1647,7 +1675,11 @@
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The user interface requires major improvement." | RESOLVED - the third HUD row sat on top of the southbound traffic lane at 320x568. Collapsed to one top card plus two chips on a city block, which never has traffic under it. The junction box is now the danger indicator: open green brackets when clear, filled red triangles plus a pulsing outline when contested - a shape and motion swap, not colour alone. Red now means exactly one thing; held moved to brand blue.</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>safe-crossing</t>
@@ -1698,7 +1730,11 @@
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "Both the user interface and gameplay mechanics need improvement." | RESOLVED - swept collision with 1,600 slides swept and 0 tunnelling; all 5 boards proven solvable at the published par with every pickup inside par+2 and no reachable dead ends; cover points and gusts verified load-bearing. Skilled bot 48.7% against random 0.0%. Survives the full 120s clock at every handset size.</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>slide-to-safety</t>
@@ -1749,7 +1785,11 @@
           <t>Rebuilt 2026-08-03 - BajajLife review found the experience did not feel like a game</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The current experience does not feel like a game." | REBUILT - was a stop-the-marker toy. Now real-time cover management: claims publish a size band and reveal the true value 0.72s out; cover raises slowly and drops fast, so you commit from the band and shave on the reveal. Under-cover drains security on a super-linear curve, over-cover drains budget - two opposed lose conditions. Skilled scores 13.5x random, asserted as a hard gate condition so it cannot regress into a calculator.</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>perfect-premium</t>
@@ -1800,7 +1840,11 @@
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Assigned elsewhere per the BajajLife 2026-08-03 review ("Already taken"). No work initiated.</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>steady-wings</t>
@@ -1902,7 +1946,11 @@
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The colours are too dull." | RESOLVED - resting tiles were painted as the goal hue at ~15% alpha over navy, which desaturates it, compositing nine distinct goals into nine identical mud rectangles. New opaque colorRest per goal; rest-to-lit luminance jump now 2.6-4.6x. Tile labels sub-AA -&gt; 15.56:1 via one scrim plate. Every state pairs colour with a shape (tick / X / circle-slash / strike / ring). Gate byte-identical.</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>smart-recall</t>
@@ -1953,7 +2001,11 @@
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The game objective and mechanics are unclear." | RESOLVED with zero rule changes - every microgame already declared a verb that was never shown to the player, and the failure countdown was painted underneath the HUD pills, occluded on every handset. Added a persistent instruction frame (verb chip + ask + money moment), a 12-segment progression track, captioned shield pips and a visible WAIT/GO cue. Gate numbers identical, which is the proof the rules were untouched.</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>life-rush</t>
@@ -2106,7 +2158,11 @@
           <t>Proposed 2026-07-29 - pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The assets and colour combinations are too basic." | RESOLVED - tier colours were an arbitrary rainbow, so tier 5 read as worth LESS than tier 4, and Piggy Bank outranked Gold Reserve. Replaced with a bronze-gold-platinum-diamond ladder climbing on six channels (body luminance, glow, rim pips, facets, orbiting motes, radius), none regressing. New scripts/tier-ladder.mjs guards the ranking contract and caught two contrast defects mid-build.</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>wealth-merge</t>
@@ -2157,7 +2213,11 @@
           <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a fruit-slice game; this differentiates via the protect-the-Family-Shield rule (slicing blue shield orbs is the penalty) and risk-labelled targets</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Assigned elsewhere per the BajajLife 2026-08-03 review ("Already taken"). No work initiated.</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>risk-slash</t>
@@ -2208,7 +2268,11 @@
           <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a stacking game; this differentiates via SIP milestone framing and the perfect-streak width-regrowth loop</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The user interface and stacking blocks are not properly designed." | RESOLVED - one geometry source: slabFaces() is the only description of a block shape, the renderer fills exactly those polygons and the drop is judged on exactly the same footprint. Asserted across 224 widths from 12px to 122.8px at 0.000px disagreement, so a drop that looks perfect can no longer be trimmed. Drop judged at pointerdown. Corpus compounds so the first surviving layer ends worth 9.7x the last. OPEN: casual bot wins 0.0% against skilled 96.7% - a sharp cliff, though the results screen grades in tiers rather than pass/fail.</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>sip-stack</t>
@@ -2255,7 +2319,11 @@
           <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The purpose of the game is difficult to understand." | RESOLVED by deleting, not explaining - the time-loop mechanic was competing with four unrelated ones (hazard beam, twin levers, five coins, a third gate) plus an invisible score penalty. All removed; loops 18s -&gt; 12s. An in-game objective coach replaces any instruction wall. Two traps closed: an unwinnable loop-1 chest grab, and loop 1 burning at 3s while the player was still reading. The animated how-to demo had never worked.</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>legacy-echo</t>
@@ -2302,7 +2370,11 @@
           <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The visual design is average and lacks polish." | RESOLVED - the stage left ~128px of dead canvas under the field at 390x844, with HUD pills and the mute button floating in it. Field now sized as plot + one HUD band; no letterbox at any size. Surveyor's-plot art direction with glow and pulse amplitudes reduced rather than increased. Added a goal rail - the win condition was previously only words. Trade-off: 412x700 loses 10% field height.</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>ring-fence</t>
@@ -2349,7 +2421,11 @@
           <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03 (named "Ripple Radar"): "The game and its mechanics are difficult to understand." | RESOLVED - one meaning per surface (touching the maze always walks; radar is its own button). Six-signal vocabulary defined once and distinguishable in greyscale. Only static geometry is remembered, so a live lurker never leaves a lying ghost. Darkness now governs how far ahead you can plan, not whether you can see. Fixed a round-line-cap compositing bug that rendered the whole map dotted. Gate 16 -&gt; 21 checks.</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>risk-radar</t>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -7,11 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Games Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do-Not-Repeat Catalog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remediation Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Games Tracker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do-Not-Repeat Catalog" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Games Tracker'!$A$1:$K$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Remediation Tracker'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Games Tracker'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +34,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +67,41 @@
         <fgColor rgb="00F26522"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000529B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB800"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005CCBF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7A2F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF4D4D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F4A64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007CD41F"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -88,6 +130,27 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,6 +516,3421 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Game Concept</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Reference Game Link</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Financial Concept</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Game Name</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Game Name Bajaj</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Feedback on Reference Game</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Game Feedback</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Directory</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Remediation Type</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>Dev Port</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
+        <is>
+          <t>Build Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cover / Shield Placement Physics (Cover Orange style)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://poki.com/en/g/cover-orange</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Preemptive risk protection</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Umbrella Cover</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Guardian Shelter</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Replace cloud with risk (virus)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>guardian-shelter</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>F — from scratch</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>8d</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream C</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>5030</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Built - polish pass done</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Bloxorz-style block rolling puzzle</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coolmathgames.com/0-bloxorz</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Bridging coverage gaps in life journey</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Balance Block Journey</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Balance Block Journey</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Dont use stages just keep one stage with longer process but time limit should be 2min max</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>balance-block-journey</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>F — never built, new build</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Phase 4 — never built</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>5031</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Not started - no directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Forward-rail crowd shooter (Battle Brigade / Mob Control style)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/battle-brigade</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Building a stable bridge for long-term wealth</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Battle Brigade</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Secure Journey</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Replace army with virus and powerup with health shield that increases the firing power</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>secure-journey</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>M+A — virus HP tiers, real powerups</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream B</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>5032</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Built - DPR fix applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Triple-tile matching (Goods Triple Match 3D style)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/goods-triple-match-3d</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Matching the Life goals</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Smart Match 3D</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Smart Match 3D</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Replace with Life goals: Shield, Savings, Home, Car, Education, Marriage, Child, Retirement, Health, Rewards, Family. Use better Assets for this not emoji</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>smart-match-3d</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>A — asset swap</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 — proving trio</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>5033</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Built - polish pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Arrow sliding escape puzzle (Arrow Exit style)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/arrow-exit-puzzle</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Smart decisions</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Arrow Escape</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Risk Exit</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Make similar game</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>risk-exit</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>F — from scratch</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream C</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>5034</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Built - polish pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Hang glider / canyon gliding (Canyon Glider style)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://kbhgames.com/game/canyon-glider</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Life-stage protection &amp; wealth collection</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Life Soar</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Life Soar</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Reference not opening - rebuilt from concept description</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>life-soar</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>M+A — mechanics redesign + assets</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream B</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>5035</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Built - polish pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Physics cannon destruction (Roly-Poly Cannon style)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>http://www.xgenstudios.com/game.php?keyword=rolypolycannon</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Risk structure elimination &amp; rebuilding</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Shield Cascade</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Shield Cascade</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Reference not opening - rebuilt from concept description</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>shield-cascade</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>F — never built, new build</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8d</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Phase 4 — never built</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>5036</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Not started - no directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Tarzan rope-swing physics traversal (original, rope-swing-style)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Bridging life's gaps - momentum of continuous protection</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Rope Swing</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Swing to Secure</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>swing-to-secure</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>M+U+A — mechanics, UI, assets</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream B</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>5037</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Crossy Road / Frogger lane-hopping (original, Crossy-Road-style)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Navigating life's risks to reach each life milestone</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Life Crossing</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Milestone Hopper</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The overall quality is below the expected standard." | RESOLVED - the hop was bound to the kit onTap, which fires on pointerup and charged every input the full 60-150ms contact; onSwipe was also wired, so one gesture fired two hops; and nothing checked destination occupancy, so ~35% of blind forward hops died with no counterplay. Casual win 46.0 -&gt; 58.5%, brisk 56.0 -&gt; 73.0%. Six milestones now bank a real corpus. The old debt sprite read as a handbag - rebuilt.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>milestone-hopper</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>M+A — mechanics redesign + assets</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5d</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 — proving trio</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>5038</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: hop moved onTap-&gt;pointerdown, double-fire and unavoidable-death fixed; casual 46-&gt;58.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>1010! drag-and-place block puzzle (no gravity)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Asset allocation - fitting every asset class into a balanced portfolio</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Block Fit 1010</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Fit</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>portfolio-fit</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>A — asset swap</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream A</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>5044</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean (restored)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Helix-jump descending ball</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Riding market cycles - descend through volatility, avoid the crash zones</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Helix Descent</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Spiral Sprint</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>spiral-sprint</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>A+U+M — assets, UI, longer run</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4d</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream A</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>5048</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Plinko / pachinko board drop</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Market volatility &amp; ULIP - disciplined investing through ups and downs</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Plinko Pachinko</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Drop</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>wealth-drop</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>A+U — asset swap + UI rebuild</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3d</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2 — proving trio</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>5039</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Jenga-style block removal without toppling</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>De-risking your portfolio without destabilizing your life plan</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Jenga De-Risk</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Steady Tower</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>steady-tower</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>A+U — asset swap + UI rebuild</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3d</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream A</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>5047</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Orbit-switch timing arcade</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Staying on track - disciplined orbit around your life goals</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Orbit Hop</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Goal Orbit</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>goal-orbit</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>B — blocked</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Awaiting client call ("need to be discussed")</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>5050</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Flick bowling physics</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Knock out risks in one decisive shot - comprehensive cover</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Shield Bowling</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Risk Strike</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>risk-strike</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>A+U — asset swap + UI rebuild</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3d</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream A</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>5054</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Pinball flippers (portrait single-screen table)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Keeping the family's cover in play - every save at the flippers is a premium paid on time</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Premium Pinball</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Premium Pinball</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>premium-pinball</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>5055</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Cricket batting timing (tap-to-swing chase)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Every ball is a life event - cover it with the right timing</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Cover Drive</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: batter misplaced, cannot hit reliably, collision inaccurate, no insurance objective, result screen off-template. | RESOLVED - there was NO collision test at all; shots were scored purely on tap timing against authored windows. Measured over 7,200 seeded deliveries, the blade actually touched the ball on 4.3% of the shots the game scored as hits. Replaced with swept segment-segment collision: 4450/4450 perfectly-timed swings now connect and middle. Four insurance zones with shaped payouts (Guaranteed Income provably cannot win alone). Result screen brought onto the shared template. EMAIL FIELD DELIBERATELY NOT ADDED - superseded by the repo-wide Name+Mobile decision.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>cover-drive</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>5056</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: swept bat/ball collision added (there was none; 4.3% of "hits" touched the blade); 4450/4450 perfect swings connect</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Steer a decaying cover span; renew before the event locks</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Cover is bought in advance, lapses if unrenewed, and never stretches over everything at once</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Goal Keeper</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Goal Keeper</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Rebuilt 2026-08-03 - BajajLife review found the original concept and execution incorrect</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The entire game concept and execution are incorrect", and separately (as "Goal Area") "looks completely AI-generated and lacks visual identity". Both notes are this one game. | REBUILT - the cover span, whose half-width IS the sum assured, decays every second and is renewable only before the event locks at 55% of ball flight. Measured: perfect positioning while never renewing wins 0.0%; identical positioning with renewals wins 99.3%. The reaction sweep is deliberately flat, so cover management separates players, not reflexes.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>goal-keeper</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>5057</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Rebuilt - 2026-08-03 review: cover-span mechanic; never-renew 0.0% vs renew 99.3%; gate PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Carrom flick-pocket physics (drag striker, pull to aim)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Pocket every goal - the Queen of Protection only stays yours if you cover her</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Carrom</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Carrom</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: weak carrom design, no bot opponent, no proper sliding/flicking control. | RESOLVED - the controls and fixed-step physics already existed and worked; they were re-verified rather than rewritten. The bot genuinely did not exist: the ghost-ball planner was imported only by the balance sim, never by the shipped bundle, so the game was solo score-attack. Bot now ships at three difficulties (89.4 / 71.9 / 55.0% against a skilled reference, random 21.3 / 11.3 / 5.0%). Anti-tunnelling proven by swept closest-approach: 880 max-power strikes, 452,813 ticks, 0 pass-throughs. 0 draws in 960 matches.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>wealth-carrom</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>5058</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: bot opponent shipped, 0 tunnelling in 452,813 ticks; 89.4/71.9/55.0% by difficulty</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Goal-funding triage with forecast shocks and a fixed-premium cover decision</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>A fixed premium against a proportional loss - cover is worth buying on the big position, not the small one</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Balloon</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Balloon</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Mechanic replaced 2026-08-03 - BajajLife review found press-your-luck provided no meaningful value; the old gate measured a zero-information bot at 55% of the skilled score</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The selected game format does not provide meaningful value." | MECHANIC REPLACED - the old gate condemned it: a bot with zero information scored 55% of the skilled result, because hold-and-release has one degree of freedom per round. A hidden random burst threshold also told players their money evaporates unpredictably, the wrong message for an insurer. Now goal-funding triage with shocks forecast 4s ahead and a fixed-premium cover decision. Skill gap 17.4pp -&gt; 87.5pp.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>wealth-balloon</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>5059</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Rebuilt - 2026-08-03 review: press-your-luck replaced with goal triage; skill gap 17.4pp -&gt; 87.5pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Pipe-rotation flow routing puzzle</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Route every rupee of income to the goals that matter - seal the leaks before payday flows</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Income Pipeline</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Income Pipeline</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The game is not functioning." | RESOLVED - no crash; it built clean and passed its gate while ending the run ~18s in, because a dry board called endRun and level 1 had an 18s clock, so boards 2 and 3 never appeared. A dry board now costs the level only; timers 26/28/32s; win bar moved off all-six-tanks (even the greedy bot clears that only 78% of the time). Run 18s -&gt; 91s.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>income-pipeline</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>5060</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review fix: run no longer ends on a dry level 1 (18s -&gt; 91s); gate 82.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Conveyor swipe-sorting (protect / grow / bin)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Protect it, grow it, or bin it - sort your money life before it scrolls past</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Smart Sorter</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Smart Sorter</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The game is not working." | RESOLVED - no crash, and input was fine (a scripted drag moved the score). 3 lives against 12 unfamiliar item types at 1.9s/card killed a first-timer on the opening three cards; run over in 11s. Added a 3-card grace that still flashes red and breaks combo but cannot spend a life. Budget stays 3 - raising it to 5 sent the casual bot to 83.4%, outside the 25-45% band.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>smart-sorter</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>5061</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review fix: 3-card mistake grace (11s -&gt; 19s); gate PASS, casual 41.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Traffic-control tap go/stop (junction management)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Life's traffic never stops - one Claim Cushion, and after that timing is everything</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Safe Crossing</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Safe Crossing</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The user interface requires major improvement." | RESOLVED - the third HUD row sat on top of the southbound traffic lane at 320x568. Collapsed to one top card plus two chips on a city block, which never has traffic under it. The junction box is now the danger indicator: open green brackets when clear, filled red triangles plus a pulsing outline when contested - a shape and motion swap, not colour alone. Red now means exactly one thing; held moved to brand blue.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>safe-crossing</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>5062</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: HUD off the traffic lane, bracket/triangle danger read; gate PASS unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Ice-slide pathing puzzle (swipe, glide to wall)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>One swipe at a time, glide your shield past thin ice and bring it home to the family</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Slide to Safety</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Slide to Safety</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "Both the user interface and gameplay mechanics need improvement." | RESOLVED - swept collision with 1,600 slides swept and 0 tunnelling; all 5 boards proven solvable at the published par with every pickup inside par+2 and no reachable dead ends; cover points and gusts verified load-bearing. Skilled bot 48.7% against random 0.0%. Survives the full 120s clock at every handset size.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>slide-to-safety</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>5063</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: swept collision, 1600 slides 0 tunnelling; skilled 48.7% / random 0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Rate-limited cover-level management against partially-hidden incoming claims</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Under-insuring is cheap until the event arrives; over-insuring is safe but spends money the goals needed</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Perfect Premium</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Perfect Premium</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Rebuilt 2026-08-03 - BajajLife review found the experience did not feel like a game</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The current experience does not feel like a game." | REBUILT - was a stop-the-marker toy. Now real-time cover management: claims publish a size band and reveal the true value 0.72s out; cover raises slowly and drops fast, so you commit from the band and shave on the reveal. Under-cover drains security on a super-linear curve, over-cover drains budget - two opposed lose conditions. Skilled scores 13.5x random, asserted as a hard gate condition so it cannot regress into a calculator.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>perfect-premium</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>5064</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Rebuilt - 2026-08-03 review: real-time cover management; skilled scores 13.5x random</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>One-tap impulse flight through gates (flappy-style)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Life's expenses keep coming - keep your cover airborne and glide through every one</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Steady Wings</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Steady Wings</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Assigned elsewhere per the BajajLife 2026-08-03 review ("Already taken"). No work initiated.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>steady-wings</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>5065</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Beat-synchronised rhythm tapping (radial go/no-go)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>A premium on every beat - stay in rhythm, skip the temptations, and cover never misses</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Premium Pulse</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Premium Pulse</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>premium-pulse</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>5066</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Built - review clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Simon-style serial sequence recall (ordered memory)</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>A financial plan only works if you remember every step - recall it in order, skip the risky detours</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Smart Recall</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Smart Recall</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The colours are too dull." | RESOLVED - resting tiles were painted as the goal hue at ~15% alpha over navy, which desaturates it, compositing nine distinct goals into nine identical mud rectangles. New opaque colorRest per goal; rest-to-lit luminance jump now 2.6-4.6x. Tile labels sub-AA -&gt; 15.56:1 via one scrim plate. Every state pairs colour with a shape (tick / X / circle-slash / strike / ring). Gate byte-identical.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>smart-recall</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>5067</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: opaque colorRest palette, labels sub-AA -&gt; 15.56:1; gate byte-identical</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>WarioWare-style microgame rush (3-5s one-verb challenges)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Life comes at you fast - pay, protect, pick and plan in seconds; that is what good cover feels like</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Life Rush</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Life Rush</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Approved - new original concept</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The game objective and mechanics are unclear." | RESOLVED with zero rule changes - every microgame already declared a verb that was never shown to the player, and the failure countdown was painted underneath the HUD pills, occluded on every handset. Added a persistent instruction frame (verb chip + ask + money moment), a 12-segment progression track, captioned shield pips and a visible WAIT/GO cue. Gate numbers identical, which is the proof the rules were untouched.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>life-rush</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>5069</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: persistent instruction frame, countdown un-occluded; gate identical (rules unchanged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Archero-style arena survivor (stop-to-shoot, wave upgrades)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/app/archero/id1453651052</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Layered protection - every upgrade between waves is another rider on the family's cover</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Guardian Arena</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Guardian Arena</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>guardian-arena</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>5070</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Piano Tiles-style 4-lane melody tapper</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/app/piano-tiles-2/id1027688889</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>A premium on every note - never miss a payment and the family's plan plays like music</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Premium Tiles</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Premium Tiles</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: an earlier premium-tiles concept was removed in the 2026-07-28 scope cut for lacking sign-off; this is a fresh implementation of the explicitly requested piano-tiles genre</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>premium-tiles</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>5071</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Suika-style drop-and-merge collector (physics jar)</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/app/suika-game-aladdin-x/id6444114954</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Compounding in your hands - small savings merge into life goals</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Merge</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Merge</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The assets and colour combinations are too basic." | RESOLVED - tier colours were an arbitrary rainbow, so tier 5 read as worth LESS than tier 4, and Piggy Bank outranked Gold Reserve. Replaced with a bronze-gold-platinum-diamond ladder climbing on six channels (body luminance, glow, rim pips, facets, orbiting motes, radius), none regressing. New scripts/tier-ladder.mjs guards the ranking contract and caught two contrast defects mid-build.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>wealth-merge</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>5072</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: bronze-&gt;diamond tier ladder (tier 5 used to read below tier 4); gate PASS + new tier-ladder guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Fruit Ninja-style swipe slicer (slash risks, spare shields)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/app/fruit-ninja/id362949845</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Cut the risks out of the family's life - cover is the blade</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Risk Slash</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Risk Slash</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a fruit-slice game; this differentiates via the protect-the-Family-Shield rule (slicing blue shield orbs is the penalty) and risk-labelled targets</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Assigned elsewhere per the BajajLife 2026-08-03 review ("Already taken"). No work initiated.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>risk-slash</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>5073</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Built - pending BajajLife sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Ketchapp Stack-style timing tower (trim on miss, regrow on perfects)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/app/stack/id1080487957</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Every layer is a monthly SIP - discipline compounds, and consistency repairs old mistakes</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>SIP Stack</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>SIP Stack</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a stacking game; this differentiates via SIP milestone framing and the perfect-streak width-regrowth loop</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The user interface and stacking blocks are not properly designed." | RESOLVED - one geometry source: slabFaces() is the only description of a block shape, the renderer fills exactly those polygons and the drop is judged on exactly the same footprint. Asserted across 224 widths from 12px to 122.8px at 0.000px disagreement, so a drop that looks perfect can no longer be trimmed. Drop judged at pointerdown. Corpus compounds so the first surviving layer ends worth 9.7x the last. OPEN: casual bot wins 0.0% against skilled 96.7% - a sharp cliff, though the results screen grades in tiers rather than pass/fail.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>sip-stack</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>5074</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: draw/collision geometry unified (224/224 at 0.000px); gate PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Time-loop past-self co-op (previous runs replay as live ghost helpers)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Your past contributions keep working for you - every premium your past self paid protects the family today</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Legacy Echo</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Legacy Echo</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The purpose of the game is difficult to understand." | RESOLVED by deleting, not explaining - the time-loop mechanic was competing with four unrelated ones (hazard beam, twin levers, five coins, a third gate) plus an invisible score penalty. All removed; loops 18s -&gt; 12s. An in-game objective coach replaces any instruction wall. Two traps closed: an unwinnable loop-1 chest grab, and loop 1 burning at 3s while the player was still reading. The animated how-to demo had never worked.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>legacy-echo</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>5075</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: four competing mechanics deleted, in-game objective coach; gate 8/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Qix/JezzBall territory capture (claim ground, wall risks out)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Ring-fence the family's wealth - a real asset-protection term made playable</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Ring-Fence</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Ring-Fence</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03: "The visual design is average and lacks polish." | RESOLVED - the stage left ~128px of dead canvas under the field at 390x844, with HUD pills and the mute button floating in it. Field now sized as plot + one HUD band; no letterbox at any size. Surveyor's-plot art direction with glow and pulse amplitudes reduced rather than increased. Added a goal rail - the win condition was previously only words. Trade-off: 412x700 loses 10% field height.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>ring-fence</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>5077</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: 128px dead strip removed, surveyor art direction; gate PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Darkness + sonar pulse navigation (perception as a resource)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>You cannot see risks coming - your cover can; send the radar, read the danger, walk the family home</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Risk Radar</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Risk Radar</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>BajajLife 2026-08-03 (named "Ripple Radar"): "The game and its mechanics are difficult to understand." | RESOLVED - one meaning per surface (touching the maze always walks; radar is its own button). Six-signal vocabulary defined once and distinguishable in greyscale. Only static geometry is remembered, so a live lurker never leaves a lying ghost. Darkness now governs how far ahead you can plan, not whether you can see. Fixed a round-line-cap compositing bug that rendered the whole map dotted. Gate 16 -&gt; 21 checks.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>risk-radar</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>A — style-guide conformance</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Phase 5 — conformance sweep</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>5078</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Built - 2026-08-03 review: signal vocabulary, dotted-map compositing bug fixed; gate 16-&gt;21 checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Archery / angle shooter (Bowman style)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/game/bowman</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Precision coverage against risks</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Coverage Archer</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Guardian Archer</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>coverage-archer</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>M+A — physics retune, single-player</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream C</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Revamp</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>Built - Phaser audit pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Balance runner on a wire</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miniplay.com/game/bug-on-a-wire</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Balancing family finances &amp; risks</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Wire Runner / Balance Dodger</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Tightrope Protection</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>tightrope-protection</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>M+A — restore wire, crows to virus</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Phase 3 — stream C</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Revamp</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Built - Phaser audit pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Bubble shooter — launch and pop colour-matched bubbles</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Deployed in bajaj-game-store (life-goals-bubble-shooter)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Goal-linked play — clear the board, clear the goal</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Life Goals Bubble Shooter</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Bubble Shooter</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED — the only title signed off in the 2026-08 review</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Approved. Portfolio-wide rules still apply: strip instructional text, remove email field, no emoji, hazards become the green virus. Do not touch the game loop.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>life-goals-bubble-shooter (bajaj-game-store repo)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>A — portfolio rules only</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Approved — conformance sweep only</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Deployed in bajaj-game-store</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>One-tap chain reaction — a single tap triggers a spreading burst</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Original concept</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>One decision protects the whole chain</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Ripple Shield</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Ripple Shield</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08 review: "Design is too simple and basic, change it totally"</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>DIRECTORY DELETED 2026-08-03 (port 5046 retired) — the deletion predates this feedback. RECOMMEND: let the deletion stand and use the slot for a new concept. Rebuilding a title the client already rejected costs the same as a fresh concept with none of the baggage. Awaiting your call.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>ripple-shield (deleted)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>F — from scratch, or drop (recommended)</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>8d / 0d</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Decision needed — rebuild or let deletion stand</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Deleted</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5046 (retired)</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Deleted 2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Magnet polarity steering — one tap flips attract/repel to steer a drifting orb</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Original concept — from scratch</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>The right pull at the right moment: cover attracts what you keep and repels what you don't</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Polarity</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Pull &amp; Protect</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-08-22 — pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>polarity-cover</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>N — new concept</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="K43" s="12" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Proposed — build after Phase 2 validates style guide</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>5080</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Load-balancing beam — drag a counterweight to keep a pivoting beam level</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Original concept — from scratch</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>A portfolio is a beam: shocks land on one side, you rebalance rather than panic-sell</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Even Keel</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Steady Balance</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-08-22 — pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>even-keel</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>N — new concept</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>5d</t>
+        </is>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Proposed — build after Phase 2 validates style guide</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>5081</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Service-queue time management — tap a customer, tap the matching life-goal token</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Original concept — from scratch</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Needs-based advice: the right cover for the right person, before they walk</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Front Desk</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Advisor Rush</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-08-22 — pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>COMPLIANCE: depicts advice — keep tokens abstract, route to legal before submission</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>front-desk</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>N — new concept</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Proposed — needs legal review before build</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>5082</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Gear-train assembly — drag gears onto pegs to drive an output wheel at a target ratio</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Original concept — from scratch</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>A plan only works if every part turns the next one</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Clockwork</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Plan in Motion</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-08-22 — pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>clockwork-plan</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>N — new concept</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Proposed — build after Phase 2 validates style guide</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>5083</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Graph untangling — drag nodes until no connecting cord crosses another</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Original concept — from scratch</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Tangled finances hide risk; straighten the lines and you can see what you own</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Untangle</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Sort My Money</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Proposed 2026-08-22 — pending BajajLife sign-off</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>untangle</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>N — new concept</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>5d</t>
+        </is>
+      </c>
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Proposed — cheapest new build, best single-glance differentiator</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>5084</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O47"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2549,13 +6027,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2634,6 +6112,18 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>New concepts (2026-08-22, pending sign-off)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>polarity-cover (magnet attract/repel steering), even-keel (load-balancing beam), front-desk (service-queue time management), clockwork-plan (gear-train assembly), untangle (graph planarity). Mechanic families deliberately chosen as unused across both this repo and bajaj-game-store.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -12,7 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do-Not-Repeat Catalog" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Remediation Tracker'!$A$1:$O$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Games Tracker'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +37,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="13">
@@ -115,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -151,6 +153,7 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -516,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -531,3396 +534,2783 @@
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Game Concept</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Reference Game Link</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Financial Concept</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Game Name</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Game Name Bajaj</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Feedback on Reference Game</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Game Feedback</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Directory</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Remediation Type</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="N1" s="6" t="inlineStr">
-        <is>
-          <t>Dev Port</t>
-        </is>
-      </c>
-      <c r="O1" s="6" t="inlineStr">
-        <is>
-          <t>Build Log</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Cover / Shield Placement Physics (Cover Orange style)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>https://poki.com/en/g/cover-orange</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Preemptive risk protection</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Umbrella Cover</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Guardian Shelter</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Ok, Replace cloud with risk (virus)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>guardian-shelter</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>F — from scratch</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>8d</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Phase 3 — stream C</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>5030</v>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Built - polish pass done</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Bloxorz-style block rolling puzzle</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>https://www.coolmathgames.com/0-bloxorz</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bridging coverage gaps in life journey</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Balance Block Journey</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Balance Block Journey</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Ok, Dont use stages just keep one stage with longer process but time limit should be 2min max</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>balance-block-journey</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>F — never built, new build</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>7d</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Phase 4 — never built</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>5031</v>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Not started - no directory</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Forward-rail crowd shooter (Battle Brigade / Mob Control style)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.crazygames.com/game/battle-brigade</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Building a stable bridge for long-term wealth</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Battle Brigade</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Secure Journey</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Ok, Replace army with virus and powerup with health shield that increases the firing power</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>secure-journey</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>M+A — virus HP tiers, real powerups</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>7d</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Phase 3 — stream B</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>5032</v>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Built - DPR fix applied</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Triple-tile matching (Goods Triple Match 3D style)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.crazygames.com/game/goods-triple-match-3d</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Matching the Life goals</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Smart Match 3D</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Smart Match 3D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Ok, Replace with Life goals: Shield, Savings, Home, Car, Education, Marriage, Child, Retirement, Health, Rewards, Family. Use better Assets for this not emoji</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>smart-match-3d</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>A — asset swap</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Phase 2 — proving trio</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>5033</v>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Built - polish pending</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Arrow sliding escape puzzle (Arrow Exit style)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.crazygames.com/game/arrow-exit-puzzle</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Smart decisions</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Arrow Escape</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Risk Exit</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Ok, Make similar game</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>risk-exit</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>F — from scratch</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>7d</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Phase 3 — stream C</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>5034</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Built - polish pending</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Hang glider / canyon gliding (Canyon Glider style)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://kbhgames.com/game/canyon-glider</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Life-stage protection &amp; wealth collection</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Life Soar</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Life Soar</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Reference not opening - rebuilt from concept description</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>life-soar</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>M+A — mechanics redesign + assets</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Phase 3 — stream B</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>5035</v>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Built - polish pending</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Physics cannon destruction (Roly-Poly Cannon style)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>http://www.xgenstudios.com/game.php?keyword=rolypolycannon</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Risk structure elimination &amp; rebuilding</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Shield Cascade</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Shield Cascade</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Reference not opening - rebuilt from concept description</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>shield-cascade</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>F — never built, new build</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>8d</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Phase 4 — never built</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>5036</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Not started - no directory</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Tarzan rope-swing physics traversal (original, rope-swing-style)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Bridging life's gaps - momentum of continuous protection</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Rope Swing</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Swing to Secure</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>swing-to-secure</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>M+U+A — mechanics, UI, assets</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Phase 3 — stream B</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>5037</v>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Built - review clean</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Crossy Road / Frogger lane-hopping (original, Crossy-Road-style)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Navigating life's risks to reach each life milestone</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Life Crossing</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Milestone Hopper</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The overall quality is below the expected standard." | RESOLVED - the hop was bound to the kit onTap, which fires on pointerup and charged every input the full 60-150ms contact; onSwipe was also wired, so one gesture fired two hops; and nothing checked destination occupancy, so ~35% of blind forward hops died with no counterplay. Casual win 46.0 -&gt; 58.5%, brisk 56.0 -&gt; 73.0%. Six milestones now bank a real corpus. The old debt sprite read as a handbag - rebuilt.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>milestone-hopper</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>M+A — mechanics redesign + assets</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Phase 2 — proving trio</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>5038</v>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: hop moved onTap-&gt;pointerdown, double-fire and unavoidable-death fixed; casual 46-&gt;58.5%</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1010! drag-and-place block puzzle (no gravity)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Asset allocation - fitting every asset class into a balanced portfolio</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Block Fit 1010</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Portfolio Fit</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Ok</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>portfolio-fit</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>A — asset swap</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Phase 3 — stream A</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>5044</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Built - review clean (restored)</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Helix-jump descending ball</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Riding market cycles - descend through volatility, avoid the crash zones</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Helix Descent</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Spiral Sprint</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>spiral-sprint</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>A+U+M — assets, UI, longer run</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Phase 3 — stream A</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>5048</v>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Built - review clean</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Plinko / pachinko board drop</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Market volatility &amp; ULIP - disciplined investing through ups and downs</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Plinko Pachinko</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Wealth Drop</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>wealth-drop</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>A+U — asset swap + UI rebuild</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Phase 2 — proving trio</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>5039</v>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Built - review clean</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Jenga-style block removal without toppling</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
         <is>
           <t>De-risking your portfolio without destabilizing your life plan</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Jenga De-Risk</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Steady Tower</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>steady-tower</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>A+U — asset swap + UI rebuild</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Phase 3 — stream A</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>5047</v>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Built - review clean</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Orbit-switch timing arcade</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Staying on track - disciplined orbit around your life goals</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Orbit Hop</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Goal Orbit</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>goal-orbit</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>B — blocked</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K15" s="10" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Awaiting client call ("need to be discussed")</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>5050</v>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Built - review clean</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Flick bowling physics</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Knock out risks in one decisive shot - comprehensive cover</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Shield Bowling</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Risk Strike</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>risk-strike</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>A+U — asset swap + UI rebuild</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Phase 3 — stream A</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>5054</v>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Built - review clean</t>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Pinball flippers (portrait single-screen table)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Keeping the family's cover in play - every save at the flippers is a premium paid on time</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Premium Pinball</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Premium Pinball</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>premium-pinball</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>5055</v>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Built - review clean</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Cricket batting timing (tap-to-swing chase)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Every ball is a life event - cover it with the right timing</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Cover Drive</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Cover Drive</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: batter misplaced, cannot hit reliably, collision inaccurate, no insurance objective, result screen off-template. | RESOLVED - there was NO collision test at all; shots were scored purely on tap timing against authored windows. Measured over 7,200 seeded deliveries, the blade actually touched the ball on 4.3% of the shots the game scored as hits. Replaced with swept segment-segment collision: 4450/4450 perfectly-timed swings now connect and middle. Four insurance zones with shaped payouts (Guaranteed Income provably cannot win alone). Result screen brought onto the shared template. EMAIL FIELD DELIBERATELY NOT ADDED - superseded by the repo-wide Name+Mobile decision.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>cover-drive</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>5056</v>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: swept bat/ball collision added (there was none; 4.3% of "hits" touched the blade); 4450/4450 perfect swings connect</t>
-        </is>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Steer a decaying cover span; renew before the event locks</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Cover is bought in advance, lapses if unrenewed, and never stretches over everything at once</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Goal Keeper</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Goal Keeper</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Rebuilt 2026-08-03 - BajajLife review found the original concept and execution incorrect</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The entire game concept and execution are incorrect", and separately (as "Goal Area") "looks completely AI-generated and lacks visual identity". Both notes are this one game. | REBUILT - the cover span, whose half-width IS the sum assured, decays every second and is renewable only before the event locks at 55% of ball flight. Measured: perfect positioning while never renewing wins 0.0%; identical positioning with renewals wins 99.3%. The reaction sweep is deliberately flat, so cover management separates players, not reflexes.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>goal-keeper</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>5057</v>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Rebuilt - 2026-08-03 review: cover-span mechanic; never-renew 0.0% vs renew 99.3%; gate PASS</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Carrom flick-pocket physics (drag striker, pull to aim)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Pocket every goal - the Queen of Protection only stays yours if you cover her</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Wealth Carrom</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Wealth Carrom</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: weak carrom design, no bot opponent, no proper sliding/flicking control. | RESOLVED - the controls and fixed-step physics already existed and worked; they were re-verified rather than rewritten. The bot genuinely did not exist: the ghost-ball planner was imported only by the balance sim, never by the shipped bundle, so the game was solo score-attack. Bot now ships at three difficulties (89.4 / 71.9 / 55.0% against a skilled reference, random 21.3 / 11.3 / 5.0%). Anti-tunnelling proven by swept closest-approach: 880 max-power strikes, 452,813 ticks, 0 pass-throughs. 0 draws in 960 matches.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>wealth-carrom</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>5058</v>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: bot opponent shipped, 0 tunnelling in 452,813 ticks; 89.4/71.9/55.0% by difficulty</t>
-        </is>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Goal-funding triage with forecast shocks and a fixed-premium cover decision</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>A fixed premium against a proportional loss - cover is worth buying on the big position, not the small one</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Wealth Balloon</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Wealth Balloon</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Mechanic replaced 2026-08-03 - BajajLife review found press-your-luck provided no meaningful value; the old gate measured a zero-information bot at 55% of the skilled score</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The selected game format does not provide meaningful value." | MECHANIC REPLACED - the old gate condemned it: a bot with zero information scored 55% of the skilled result, because hold-and-release has one degree of freedom per round. A hidden random burst threshold also told players their money evaporates unpredictably, the wrong message for an insurer. Now goal-funding triage with shocks forecast 4s ahead and a fixed-premium cover decision. Skill gap 17.4pp -&gt; 87.5pp.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>wealth-balloon</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>5059</v>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Rebuilt - 2026-08-03 review: press-your-luck replaced with goal triage; skill gap 17.4pp -&gt; 87.5pp</t>
-        </is>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Pipe-rotation flow routing puzzle</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Route every rupee of income to the goals that matter - seal the leaks before payday flows</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Income Pipeline</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Income Pipeline</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The game is not functioning." | RESOLVED - no crash; it built clean and passed its gate while ending the run ~18s in, because a dry board called endRun and level 1 had an 18s clock, so boards 2 and 3 never appeared. A dry board now costs the level only; timers 26/28/32s; win bar moved off all-six-tanks (even the greedy bot clears that only 78% of the time). Run 18s -&gt; 91s.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>income-pipeline</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>5060</v>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review fix: run no longer ends on a dry level 1 (18s -&gt; 91s); gate 82.3%</t>
-        </is>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Conveyor swipe-sorting (protect / grow / bin)</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Protect it, grow it, or bin it - sort your money life before it scrolls past</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Smart Sorter</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Smart Sorter</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The game is not working." | RESOLVED - no crash, and input was fine (a scripted drag moved the score). 3 lives against 12 unfamiliar item types at 1.9s/card killed a first-timer on the opening three cards; run over in 11s. Added a 3-card grace that still flashes red and breaks combo but cannot spend a life. Budget stays 3 - raising it to 5 sent the casual bot to 83.4%, outside the 25-45% band.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>smart-sorter</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>5061</v>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review fix: 3-card mistake grace (11s -&gt; 19s); gate PASS, casual 41.6%</t>
-        </is>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Traffic-control tap go/stop (junction management)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Life's traffic never stops - one Claim Cushion, and after that timing is everything</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Safe Crossing</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Safe Crossing</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The user interface requires major improvement." | RESOLVED - the third HUD row sat on top of the southbound traffic lane at 320x568. Collapsed to one top card plus two chips on a city block, which never has traffic under it. The junction box is now the danger indicator: open green brackets when clear, filled red triangles plus a pulsing outline when contested - a shape and motion swap, not colour alone. Red now means exactly one thing; held moved to brand blue.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>safe-crossing</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>5062</v>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: HUD off the traffic lane, bracket/triangle danger read; gate PASS unchanged</t>
-        </is>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Ice-slide pathing puzzle (swipe, glide to wall)</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>One swipe at a time, glide your shield past thin ice and bring it home to the family</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Slide to Safety</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Slide to Safety</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "Both the user interface and gameplay mechanics need improvement." | RESOLVED - swept collision with 1,600 slides swept and 0 tunnelling; all 5 boards proven solvable at the published par with every pickup inside par+2 and no reachable dead ends; cover points and gusts verified load-bearing. Skilled bot 48.7% against random 0.0%. Survives the full 120s clock at every handset size.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>slide-to-safety</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>5063</v>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: swept collision, 1600 slides 0 tunnelling; skilled 48.7% / random 0.0%</t>
-        </is>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Rate-limited cover-level management against partially-hidden incoming claims</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Under-insuring is cheap until the event arrives; over-insuring is safe but spends money the goals needed</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Perfect Premium</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Perfect Premium</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Rebuilt 2026-08-03 - BajajLife review found the experience did not feel like a game</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The current experience does not feel like a game." | REBUILT - was a stop-the-marker toy. Now real-time cover management: claims publish a size band and reveal the true value 0.72s out; cover raises slowly and drops fast, so you commit from the band and shave on the reveal. Under-cover drains security on a super-linear curve, over-cover drains budget - two opposed lose conditions. Skilled scores 13.5x random, asserted as a hard gate condition so it cannot regress into a calculator.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>perfect-premium</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>5064</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Rebuilt - 2026-08-03 review: real-time cover management; skilled scores 13.5x random</t>
-        </is>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>One-tap impulse flight through gates (flappy-style)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Life's expenses keep coming - keep your cover airborne and glide through every one</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Steady Wings</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Steady Wings</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Assigned elsewhere per the BajajLife 2026-08-03 review ("Already taken"). No work initiated.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>steady-wings</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>5065</v>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>Built - review clean</t>
-        </is>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Beat-synchronised rhythm tapping (radial go/no-go)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>A premium on every beat - stay in rhythm, skip the temptations, and cover never misses</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Premium Pulse</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Premium Pulse</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>premium-pulse</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>5066</v>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Built - review clean</t>
-        </is>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Simon-style serial sequence recall (ordered memory)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>A financial plan only works if you remember every step - recall it in order, skip the risky detours</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Smart Recall</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Smart Recall</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The colours are too dull." | RESOLVED - resting tiles were painted as the goal hue at ~15% alpha over navy, which desaturates it, compositing nine distinct goals into nine identical mud rectangles. New opaque colorRest per goal; rest-to-lit luminance jump now 2.6-4.6x. Tile labels sub-AA -&gt; 15.56:1 via one scrim plate. Every state pairs colour with a shape (tick / X / circle-slash / strike / ring). Gate byte-identical.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>smart-recall</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>5067</v>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: opaque colorRest palette, labels sub-AA -&gt; 15.56:1; gate byte-identical</t>
-        </is>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>WarioWare-style microgame rush (3-5s one-verb challenges)</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Life comes at you fast - pay, protect, pick and plan in seconds; that is what good cover feels like</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Life Rush</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Life Rush</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Approved - new original concept</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The game objective and mechanics are unclear." | RESOLVED with zero rule changes - every microgame already declared a verb that was never shown to the player, and the failure countdown was painted underneath the HUD pills, occluded on every handset. Added a persistent instruction frame (verb chip + ask + money moment), a 12-segment progression track, captioned shield pips and a visible WAIT/GO cue. Gate numbers identical, which is the proof the rules were untouched.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>life-rush</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>5069</v>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: persistent instruction frame, countdown un-occluded; gate identical (rules unchanged)</t>
-        </is>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Archero-style arena survivor (stop-to-shoot, wave upgrades)</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>https://apps.apple.com/app/archero/id1453651052</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Layered protection - every upgrade between waves is another rider on the family's cover</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Guardian Arena</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Guardian Arena</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Proposed 2026-07-29 - pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
         <is>
           <t>guardian-arena</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>5070</v>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Built - pending BajajLife sign-off</t>
-        </is>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Piano Tiles-style 4-lane melody tapper</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>https://apps.apple.com/app/piano-tiles-2/id1027688889</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>A premium on every note - never miss a payment and the family's plan plays like music</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Premium Tiles</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Premium Tiles</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: an earlier premium-tiles concept was removed in the 2026-07-28 scope cut for lacking sign-off; this is a fresh implementation of the explicitly requested piano-tiles genre</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
         <is>
           <t>premium-tiles</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>5071</v>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Built - pending BajajLife sign-off</t>
-        </is>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Suika-style drop-and-merge collector (physics jar)</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>https://apps.apple.com/app/suika-game-aladdin-x/id6444114954</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Compounding in your hands - small savings merge into life goals</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Wealth Merge</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Wealth Merge</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Proposed 2026-07-29 - pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The assets and colour combinations are too basic." | RESOLVED - tier colours were an arbitrary rainbow, so tier 5 read as worth LESS than tier 4, and Piggy Bank outranked Gold Reserve. Replaced with a bronze-gold-platinum-diamond ladder climbing on six channels (body luminance, glow, rim pips, facets, orbiting motes, radius), none regressing. New scripts/tier-ladder.mjs guards the ranking contract and caught two contrast defects mid-build.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>wealth-merge</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>5072</v>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: bronze-&gt;diamond tier ladder (tier 5 used to read below tier 4); gate PASS + new tier-ladder guard</t>
-        </is>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Fruit Ninja-style swipe slicer (slash risks, spare shields)</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>https://apps.apple.com/app/fruit-ninja/id362949845</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Cut the risks out of the family's life - cover is the blade</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Risk Slash</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Risk Slash</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a fruit-slice game; this differentiates via the protect-the-Family-Shield rule (slicing blue shield orbs is the penalty) and risk-labelled targets</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Assigned elsewhere per the BajajLife 2026-08-03 review ("Already taken"). No work initiated.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>risk-slash</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>5073</v>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>Built - pending BajajLife sign-off</t>
-        </is>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Ketchapp Stack-style timing tower (trim on miss, regrow on perfects)</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>https://apps.apple.com/app/stack/id1080487957</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Every layer is a monthly SIP - discipline compounds, and consistency repairs old mistakes</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>SIP Stack</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>SIP Stack</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Proposed 2026-07-29 - pending BajajLife sign-off. Note: bajaj-game-store catalog lists a stacking game; this differentiates via SIP milestone framing and the perfect-streak width-regrowth loop</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The user interface and stacking blocks are not properly designed." | RESOLVED - one geometry source: slabFaces() is the only description of a block shape, the renderer fills exactly those polygons and the drop is judged on exactly the same footprint. Asserted across 224 widths from 12px to 122.8px at 0.000px disagreement, so a drop that looks perfect can no longer be trimmed. Drop judged at pointerdown. Corpus compounds so the first surviving layer ends worth 9.7x the last. OPEN: casual bot wins 0.0% against skilled 96.7% - a sharp cliff, though the results screen grades in tiers rather than pass/fail.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>sip-stack</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>5074</v>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: draw/collision geometry unified (224/224 at 0.000px); gate PASS</t>
-        </is>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Time-loop past-self co-op (previous runs replay as live ghost helpers)</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Your past contributions keep working for you - every premium your past self paid protects the family today</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Legacy Echo</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Legacy Echo</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The purpose of the game is difficult to understand." | RESOLVED by deleting, not explaining - the time-loop mechanic was competing with four unrelated ones (hazard beam, twin levers, five coins, a third gate) plus an invisible score penalty. All removed; loops 18s -&gt; 12s. An in-game objective coach replaces any instruction wall. Two traps closed: an unwinnable loop-1 chest grab, and loop 1 burning at 3s while the player was still reading. The animated how-to demo had never worked.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>legacy-echo</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>5075</v>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: four competing mechanics deleted, in-game objective coach; gate 8/8</t>
-        </is>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Qix/JezzBall territory capture (claim ground, wall risks out)</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Ring-fence the family's wealth - a real asset-protection term made playable</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Ring-Fence</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Ring-Fence</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03: "The visual design is average and lacks polish." | RESOLVED - the stage left ~128px of dead canvas under the field at 390x844, with HUD pills and the mute button floating in it. Field now sized as plot + one HUD band; no letterbox at any size. Surveyor's-plot art direction with glow and pulse amplitudes reduced rather than increased. Added a goal rail - the win condition was previously only words. Trade-off: 412x700 loses 10% field height.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>ring-fence</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>5077</v>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: 128px dead strip removed, surveyor art direction; gate PASS</t>
-        </is>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Darkness + sonar pulse navigation (perception as a resource)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
         <is>
           <t>You cannot see risks coming - your cover can; send the radar, read the danger, walk the family home</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Risk Radar</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Risk Radar</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Proposed 2026-07-30 - pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>BajajLife 2026-08-03 (named "Ripple Radar"): "The game and its mechanics are difficult to understand." | RESOLVED - one meaning per surface (touching the maze always walks; radar is its own button). Six-signal vocabulary defined once and distinguishable in greyscale. Only static geometry is remembered, so a live lurker never leaves a lying ghost. Darkness now governs how far ahead you can plan, not whether you can see. Fixed a round-line-cap compositing bug that rendered the whole map dotted. Gate 16 -&gt; 21 checks.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>risk-radar</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>A — style-guide conformance</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Phase 5 — conformance sweep</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>5078</v>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>Built - 2026-08-03 review: signal vocabulary, dotted-map compositing bug fixed; gate 16-&gt;21 checks</t>
-        </is>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Archery / angle shooter (Bowman style)</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>https://www.crazygames.com/game/bowman</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Precision coverage against risks</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Coverage Archer</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Guardian Archer</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Ok, Make single player: replace the other human opponent with virus targets; ONLY our player can fire (no return fire)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
         <is>
           <t>coverage-archer</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>M+A — physics retune, single-player</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>7d</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Phase 3 — stream C</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Revamp</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>Built - Phaser audit pending</t>
-        </is>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Balance runner on a wire</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>https://www.miniplay.com/game/bug-on-a-wire</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Balancing family finances &amp; risks</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Wire Runner / Balance Dodger</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Tightrope Protection</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Ok, Replace crows with risks {Risk = Green virus} Remove wire, it must be on flat ground.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
         <is>
           <t>tightrope-protection</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>M+A — restore wire, crows to virus</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Phase 3 — stream C</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Revamp</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>Built - Phaser audit pending</t>
-        </is>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Bubble shooter — launch and pop colour-matched bubbles</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Deployed in bajaj-game-store (life-goals-bubble-shooter)</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Goal-linked play — clear the board, clear the goal</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Life Goals Bubble Shooter</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Bubble Shooter</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>APPROVED — the only title signed off in the 2026-08 review</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Approved. Portfolio-wide rules still apply: strip instructional text, remove email field, no emoji, hazards become the green virus. Do not touch the game loop.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>life-goals-bubble-shooter (bajaj-game-store repo)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>A — portfolio rules only</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="K41" s="11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Approved — conformance sweep only</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>Deployed in bajaj-game-store</t>
-        </is>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>One-tap chain reaction — a single tap triggers a spreading burst</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Original concept</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>One decision protects the whole chain</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Ripple Shield</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Ripple Shield</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>2026-08 review: "Design is too simple and basic, change it totally"</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>DIRECTORY DELETED 2026-08-03 (port 5046 retired) — the deletion predates this feedback. RECOMMEND: let the deletion stand and use the slot for a new concept. Rebuilding a title the client already rejected costs the same as a fresh concept with none of the baggage. Awaiting your call.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>ripple-shield (deleted)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>F — from scratch, or drop (recommended)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>8d / 0d</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Decision needed — rebuild or let deletion stand</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Deleted</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>5046 (retired)</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>Deleted 2026-08-03</t>
-        </is>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Magnet polarity steering — one tap flips attract/repel to steer a drifting orb</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Original concept — from scratch</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>The right pull at the right moment: cover attracts what you keep and repels what you don't</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Polarity</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Pull &amp; Protect</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Proposed 2026-08-22 — pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
         <is>
           <t>polarity-cover</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>N — new concept</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Proposed — build after Phase 2 validates style guide</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>5080</v>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Load-balancing beam — drag a counterweight to keep a pivoting beam level</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Original concept — from scratch</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>A portfolio is a beam: shocks land on one side, you rebalance rather than panic-sell</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Even Keel</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Steady Balance</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Proposed 2026-08-22 — pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
         <is>
           <t>even-keel</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>N — new concept</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Proposed — build after Phase 2 validates style guide</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>5081</v>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Service-queue time management — tap a customer, tap the matching life-goal token</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Original concept — from scratch</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Needs-based advice: the right cover for the right person, before they walk</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Front Desk</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Advisor Rush</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Proposed 2026-08-22 — pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>COMPLIANCE: depicts advice — keep tokens abstract, route to legal before submission</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>front-desk</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>N — new concept</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>7d</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Proposed — needs legal review before build</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>5082</v>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Gear-train assembly — drag gears onto pegs to drive an output wheel at a target ratio</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Original concept — from scratch</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>A plan only works if every part turns the next one</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Clockwork</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Plan in Motion</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Proposed 2026-08-22 — pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
         <is>
           <t>clockwork-plan</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>N — new concept</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="K46" s="12" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>Proposed — build after Phase 2 validates style guide</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>5083</v>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Graph untangling — drag nodes until no connecting cord crosses another</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Original concept — from scratch</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Tangled finances hide risk; straighten the lines and you can see what you own</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Untangle</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Sort My Money</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Proposed 2026-08-22 — pending BajajLife sign-off</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
         <is>
           <t>untangle</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>N — new concept</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Proposed — cheapest new build, best single-glance differentiator</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>5084</v>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/GAMES_TRACKER.xlsx
+++ b/GAMES_TRACKER.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Phase 3 — stream C</t>
+          <t>Screens done — rebuild decision open</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Phase 2 — proving trio</t>
+          <t>Screens done — art still to swap</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Phase 3 — stream B</t>
+          <t>Screens + virus art done — mechanics open</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>A — style-guide conformance</t>
+          <t>A — asset swap</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Phase 5 — conformance sweep</t>
+          <t>Done — sprites + screens shipped</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Phase 3 — stream C</t>
+          <t>Screens + archer art done — physics open</t>
         </is>
       </c>
     </row>
